--- a/resultados/grupo_pinza_V2.xlsx
+++ b/resultados/grupo_pinza_V2.xlsx
@@ -30,6 +30,18 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="B4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Es la campaña donde la pinza ha vendido (grupo 'Pinza', 99% del gasto de la pinza). Su grupo antiguo 'Pinza' tiene estas mismas keywords: debe seguir EN PAUSA para no pujar contra ti mismo. Alternativa: campaña nueva solo para este grupo (control de presupuesto más limpio).</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B8" authorId="0">
       <text>
         <r>
@@ -127,12 +139,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="318">
   <si>
     <t xml:space="preserve">Grupo de anuncios Pinza V2 — plan de cambios y seguimiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Producto: Genérico Soporte Móvil para Coche con Pinza Ajustable 360° para Salpicadero/Parasol/Espejo Retr…  |  ASIN B0DCZS1NR6  |  SKU O8-5W7J-DSK1  |  Creado 25/09/2026</t>
+    <t xml:space="preserve">Producto: Soporte Móvil para Coche con Pinza Ajustable 360° para Salpicadero/Parasol/Espejo Retrovisor, A…  |  ASIN B0DCZS1NR6  |  SKU O8-5W7J-DSK1  |  Creado 25/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">PARÁMETROS</t>
@@ -252,7 +264,7 @@
     <t xml:space="preserve">Campaña</t>
   </si>
   <si>
-    <t xml:space="preserve">(rellenar: campaña donde se crea el grupo)</t>
+    <t xml:space="preserve">Soporte móvil pinza  (ID A0335903WCRWL9CYXAOF)</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de campaña</t>
@@ -300,7 +312,7 @@
     <t xml:space="preserve">Anuncio: Nombre</t>
   </si>
   <si>
-    <t xml:space="preserve">Genérico Soporte Móvil para Coche con Pinza Ajustable 360° para Salpicadero/Parasol/Espejo Retrovisor, Antideslizante y Estable | Compatible con iPhone, Samsung, Xiaomi y Más</t>
+    <t xml:space="preserve">Soporte Móvil para Coche con Pinza Ajustable 360° para Salpicadero/Parasol/Espejo Retrovisor, Antideslizante y Estable | Compatible con iPhone, Samsung, Xiaomi y Más</t>
   </si>
   <si>
     <t xml:space="preserve">Segmentación</t>
@@ -396,21 +408,21 @@
     <t xml:space="preserve">T-002</t>
   </si>
   <si>
+    <t xml:space="preserve">soporte móvil para coche de pinza para salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amplia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-003</t>
+  </si>
+  <si>
     <t xml:space="preserve">soporte móvil para coche de pinza</t>
   </si>
   <si>
     <t xml:space="preserve">Exacta</t>
   </si>
   <si>
-    <t xml:space="preserve">T-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soporte móvil para coche de pinza para salpicadero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amplia</t>
-  </si>
-  <si>
     <t xml:space="preserve">T-004</t>
   </si>
   <si>
@@ -441,7 +453,7 @@
     <t xml:space="preserve">T-009</t>
   </si>
   <si>
-    <t xml:space="preserve">soporte teléfono coche pinza para salpicadero</t>
+    <t xml:space="preserve">soporte móvil coche pinza ajustable</t>
   </si>
   <si>
     <t xml:space="preserve">T-010</t>
@@ -555,19 +567,19 @@
     <t xml:space="preserve">Añadir keyword (histórica)</t>
   </si>
   <si>
-    <t xml:space="preserve">Histórico: 24 clics, 6 compras, 10.78 € de gasto, 65.35 € de ventas. ACOS 16.5% &lt; 30% → subir 25%.</t>
+    <t xml:space="preserve">Histórico (suma de 2 grupos): 27 clics, 6 compras, 12.36 € de gasto, 65.35 € de ventas. ACOS 18.9% &lt; 30% → subir 25%.</t>
   </si>
   <si>
     <t xml:space="preserve">ACOS en el grupo antiguo</t>
   </si>
   <si>
-    <t xml:space="preserve">Histórico: 12 clics, 2 compras, 6.60 € de gasto, 23.98 € de ventas. ACOS 27.5% &lt; 30% → subir 25%.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Histórico: 9 clics, 1 compras, 3.12 € de gasto, 10.39 € de ventas. ACOS 30.0% en objetivo → se mantiene.</t>
   </si>
   <si>
-    <t xml:space="preserve">Histórico: 31 clics, 3 compras, 11.95 € de gasto, 32.77 € de ventas. ACOS 36.5% algo alto → bajar 10%.</t>
+    <t xml:space="preserve">Histórico (suma de 2 grupos): 14 clics, 2 compras, 7.41 € de gasto, 23.98 € de ventas. ACOS 30.9% en objetivo → se mantiene.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórico (suma de 2 grupos): 37 clics, 4 compras, 13.64 € de gasto, 43.16 € de ventas. ACOS 31.6% en objetivo → se mantiene (limitada a la puja máx. rentable 0.41€).</t>
   </si>
   <si>
     <t xml:space="preserve">Histórico: 18 clics, 2 compras, 10.83 € de gasto, 22.78 € de ventas. ACOS 47.5% &gt; 40% → bajar 25%.</t>
@@ -576,16 +588,16 @@
     <t xml:space="preserve">Añadir keyword (especial IA)</t>
   </si>
   <si>
-    <t xml:space="preserve">El modelo la da como la mejor frase nueva (11,2% compra/clic): junta 'pinza' + 'coche' (lo que más vende) con '360', una ventaja del título. Modelo: 11.2% compra/clic → puja máx. rentable 0.44 € para ACOS 35%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El retrovisor es uno de los 3 sitios de montaje del título y ninguna keyword lo cubre. Quien lo busca sabe exactamente qué quiere. Modelo: 11.9% compra/clic → puja máx. rentable 0.47 € para ACOS 35%.</t>
+    <t xml:space="preserve">Top del modelo con el histórico completo (11,4% compra/clic): junta 'pinza' + 'coche' (lo que más vende) con '360', una ventaja del título. Modelo: 11.4% compra/clic → puja máx. rentable 0.45 € para ACOS 35%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El retrovisor es uno de los 3 sitios de montaje del título y ninguna keyword lo cubre. Quien lo busca sabe exactamente qué quiere. Modelo: 12.0% compra/clic → puja máx. rentable 0.47 € para ACOS 35%.</t>
   </si>
   <si>
     <t xml:space="preserve">El parasol es otro sitio de montaje del título, sin cubrir. Búsqueda muy específica: poca competencia, intención alta. Modelo: 11.6% compra/clic → puja máx. rentable 0.46 € para ACOS 35%.</t>
   </si>
   <si>
-    <t xml:space="preserve">'Salpicadero' ya vendió (ACOS 30%). Usa 'teléfono' en vez de 'móvil' para captar a quien busca con esa palabra. Modelo: 8.6% compra/clic → puja máx. rentable 0.34 € para ACOS 35%.</t>
+    <t xml:space="preserve">Siguiente del ranking del modelo (11,6% compra/clic). 'Ajustable' es la primera característica del título. Sustituye a 'soporte teléfono … salpicadero': con el histórico completo, 'teléfono' resta ventas. Modelo: 11.6% compra/clic → puja máx. rentable 0.46 € para ACOS 35%.</t>
   </si>
   <si>
     <t xml:space="preserve">Mucha gente busca por modelo de móvil. El título dice 'compatible con iPhone': cubre esa búsqueda sin pagar por lo genérico. Modelo: 11.6% compra/clic → puja máx. rentable 0.46 € para ACOS 35%.</t>
@@ -801,7 +813,7 @@
     <t xml:space="preserve">Histórico del soporte de pinza (B0DCZS1NR6) — exports de Amazon Ads relacionados con el anuncio por totales. Base de la selección.</t>
   </si>
   <si>
-    <t xml:space="preserve">Archivo origen</t>
+    <t xml:space="preserve">Campaña / grupo de anuncios</t>
   </si>
   <si>
     <t xml:space="preserve">¿Seleccionada?</t>
@@ -813,7 +825,7 @@
     <t xml:space="preserve">En pausa (campaña)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sponsored_Products_Target_Sep_25_2026 (5).csv</t>
+    <t xml:space="preserve">Campaña - 2/5/2025 11:00:04.617 / el malo va bien :(</t>
   </si>
   <si>
     <t xml:space="preserve">Sí</t>
@@ -822,39 +834,219 @@
     <t xml:space="preserve">Top 5 por ACOS entre las que tienen ventas</t>
   </si>
   <si>
+    <t xml:space="preserve">Soporte móvil pinza / Pinza</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
     <t xml:space="preserve">ACOS 48.7%: la que más vende, pero por encima del objetivo. Su versión Exacta y Amplia rinden mejor.</t>
   </si>
   <si>
+    <t xml:space="preserve">soporte móvil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaign - 13/4/2025 9:51:56.744 / Promoción mala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACOS 193%: gasta casi 3 € por cada € vendido</t>
+  </si>
+  <si>
     <t xml:space="preserve">soporte movil coche</t>
   </si>
   <si>
-    <t xml:space="preserve">Sponsored_Products_Target_Sep_25_2026 (7).csv</t>
+    <t xml:space="preserve">Campaña con ajustes preestablecidos - B0DCZS1NR6 - 27/9/2024 19:18:30 / Grupo de anuncios - 27/9/2024 19:18:30</t>
   </si>
   <si>
     <t xml:space="preserve">ACOS 293%: gasta casi 3 € por cada € vendido</t>
   </si>
   <si>
+    <t xml:space="preserve">soporte para movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuevo producto - B0DCZS1NR6 - 21/10/2024 9:39:18 / Grupo de anuncios - 21/10/2024 9:39:18</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sin ventas</t>
   </si>
   <si>
+    <t xml:space="preserve">SP Campaign Recommendation - Suggested Products - 04/03/2025 ded33a / Genérico - Car Electronics Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujetar movil en el coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soporte pinza bruh / Grupo de anuncios - 11/1/2025 0:00:19.292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujeta moviles para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte móvil para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soporte pinza a ver / Pinza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">car mount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte móvil para coche salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soport movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte telefono 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte teléfono coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para el movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujeta móvil de pinza para coche</t>
+  </si>
+  <si>
     <t xml:space="preserve">sujeta móvil de pinza</t>
   </si>
   <si>
-    <t xml:space="preserve">sujeta móvil de pinza para coche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soporte telefono 360</t>
+    <t xml:space="preserve">soporte de móvil para coche pinza</t>
   </si>
   <si>
     <t xml:space="preserve">Sin clics: sin datos</t>
   </si>
   <si>
+    <t xml:space="preserve">suporte telemovel carro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soportes para moviles coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">car phone holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil coche iman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para telefono movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soportes para moviles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porta movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para coche para móvil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">porta telefono para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil camion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte de pinza para móvil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soport movil coch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte de móvil para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte magnetico movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil coche pinza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil coche ventosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujeción movil coche</t>
+  </si>
+  <si>
     <t xml:space="preserve">soporte movil ajustable 360</t>
   </si>
   <si>
+    <t xml:space="preserve">soporte de movil para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte mobil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil coche salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte móvil coche pinza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte móvil para salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte de móvil para coche salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para moviles coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte para móvil en coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accesorios coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enganche movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portamoviles coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte coche telefono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte de telefono para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte de teléfono para coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte gps coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil coche rejilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soporte movil salpicadero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujeta movil coche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sujetador de movil para coche</t>
+  </si>
+  <si>
     <t xml:space="preserve">soporte movil coche ajustable 360</t>
   </si>
   <si>
@@ -867,7 +1059,40 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Descartado del análisis: 'Sponsored_Products_Target_Sep_25_2026 (3).csv' (no cuadra con ningún export de anuncios; parece un export repetido de otro rango de fechas).</t>
+    <t xml:space="preserve">Fuente: FreshFinder_Amazon_Ads_historico.xlsx (rango 'Duración de la campaña'). Solo keywords de grupos donde la pinza tiene ≥ 90% del gasto:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Campaña con ajustes preestablecidos - B0DCZS1NR6 - 27/9/2024 19:18:30 / Grupo de anuncios - 27/9/2024 19:18:30 — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Campaign - 13/4/2025 9:51:56.744 / Promoción mala — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Nuevo producto - B0DCZS1NR6 - 21/10/2024 9:39:18 / Grupo de anuncios - 21/10/2024 9:39:18 — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  SP Campaign Recommendation - Suggested Products - 04/03/2025 ded33a / Genérico - Car Electronics Other — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Soporte pinza bruh / Grupo de anuncios - 11/1/2025 0:00:19.292 — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Campaña - 2/5/2025 11:00:04.617 / el malo va bien :( — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Soporte pinza a ver / Pinza — 100% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✔ usado  Soporte móvil pinza / Pinza — 99% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✘ fuera   Soporte móvil AC / Básico — 79% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ✘ fuera   Soporte móvil pinza / Salpicadero sin ventosa — 68% del gasto del grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La selección suma la misma keyword + coincidencia de todos los grupos (p. ej. 'de pinza' Amplia está en 2 grupos).</t>
   </si>
 </sst>
 </file>
@@ -2070,7 +2295,7 @@
         <v>1.17</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>88</v>
@@ -2105,7 +2330,7 @@
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W5)=0,O5,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W5,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W5))),O5)</f>
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS(Seguimiento!$G:$G,Seguimiento!$Q:$Q,W5,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W5)),0)</f>
@@ -2147,18 +2372,18 @@
         <v>87</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="P5" s="7" t="n">
         <f aca="false">ROUND(O5*(1-Leyenda!$B$11),2)</f>
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="Q5" s="7" t="n">
         <f aca="false">ROUND(O5*(1+Leyenda!$B$11),2)</f>
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="S5" s="4" t="s">
         <v>91</v>
@@ -2177,7 +2402,7 @@
       </c>
       <c r="W5" s="4" t="str">
         <f aca="false">B5&amp;" | "&amp;C5</f>
-        <v>soporte móvil para coche de pinza | Exacta</v>
+        <v>soporte móvil para coche de pinza para salpicadero | Amplia</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2193,7 +2418,7 @@
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W6)=0,O6,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W6,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W6))),O6)</f>
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS(Seguimiento!$G:$G,Seguimiento!$Q:$Q,W6,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W6)),0)</f>
@@ -2235,18 +2460,18 @@
         <v>87</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="P6" s="7" t="n">
         <f aca="false">ROUND(O6*(1-Leyenda!$B$11),2)</f>
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="Q6" s="7" t="n">
         <f aca="false">ROUND(O6*(1+Leyenda!$B$11),2)</f>
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="S6" s="4" t="s">
         <v>94</v>
@@ -2265,7 +2490,7 @@
       </c>
       <c r="W6" s="4" t="str">
         <f aca="false">B6&amp;" | "&amp;C6</f>
-        <v>soporte móvil para coche de pinza para salpicadero | Amplia</v>
+        <v>soporte móvil para coche de pinza | Exacta</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2274,14 +2499,14 @@
         <v>Activado</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W7)=0,O7,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W7,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W7))),O7)</f>
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS(Seguimiento!$G:$G,Seguimiento!$Q:$Q,W7,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W7)),0)</f>
@@ -2323,18 +2548,18 @@
         <v>87</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="P7" s="7" t="n">
         <f aca="false">ROUND(O7*(1-Leyenda!$B$11),2)</f>
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="Q7" s="7" t="n">
         <f aca="false">ROUND(O7*(1+Leyenda!$B$11),2)</f>
-        <v>0.56</v>
+        <v>0.62</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="S7" s="4" t="s">
         <v>95</v>
@@ -2365,7 +2590,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W8)=0,O8,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W8,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W8))),O8)</f>
@@ -2457,7 +2682,7 @@
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W9)=0,O9,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W9,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W9))),O9)</f>
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS(Seguimiento!$G:$G,Seguimiento!$Q:$Q,W9,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W9)),0)</f>
@@ -2499,18 +2724,18 @@
         <v>98</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="P9" s="7" t="n">
         <f aca="false">ROUND(O9*(1-Leyenda!$B$11),2)</f>
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">ROUND(O9*(1+Leyenda!$B$11),2)</f>
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="S9" s="4" t="s">
         <v>99</v>
@@ -2721,7 +2946,7 @@
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">IFERROR(IF(_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W12)=0,O12,SUMIFS(Seguimiento!$F:$F,Seguimiento!$Q:$Q,W12,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W12))),O12)</f>
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">IFERROR(SUMIFS(Seguimiento!$G:$G,Seguimiento!$Q:$Q,W12,Seguimiento!$A:$A,_xlfn.MAXIFS(Seguimiento!$A:$A,Seguimiento!$Q:$Q,W12)),0)</f>
@@ -2763,18 +2988,18 @@
         <v>98</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="P12" s="7" t="n">
         <f aca="false">ROUND(O12*(1-Leyenda!$B$11),2)</f>
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="Q12" s="7" t="n">
         <f aca="false">ROUND(O12*(1+Leyenda!$B$11),2)</f>
-        <v>0.51</v>
+        <v>0.69</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>105</v>
@@ -2793,7 +3018,7 @@
       </c>
       <c r="W12" s="4" t="str">
         <f aca="false">B12&amp;" | "&amp;C12</f>
-        <v>soporte teléfono coche pinza para salpicadero | Frase</v>
+        <v>soporte móvil coche pinza ajustable | Frase</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3129,7 +3354,7 @@
         <v>91</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="34" t="n">
         <v>0</v>
@@ -3167,11 +3392,11 @@
       </c>
       <c r="Q5" s="4" t="str">
         <f aca="false">IF(B5="","",B5&amp;" | "&amp;C5)</f>
-        <v>soporte móvil para coche de pinza | Exacta</v>
+        <v>soporte móvil para coche de pinza para salpicadero | Amplia</v>
       </c>
       <c r="R5" s="0" t="str">
         <f aca="false">IF(B5="","",Q5&amp;"#"&amp;A5)</f>
-        <v>soporte móvil para coche de pinza | Exacta#46290</v>
+        <v>soporte móvil para coche de pinza para salpicadero | Amplia#46290</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3191,7 +3416,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="G6" s="34" t="n">
         <v>0</v>
@@ -3229,11 +3454,11 @@
       </c>
       <c r="Q6" s="4" t="str">
         <f aca="false">IF(B6="","",B6&amp;" | "&amp;C6)</f>
-        <v>soporte móvil para coche de pinza para salpicadero | Amplia</v>
+        <v>soporte móvil para coche de pinza | Exacta</v>
       </c>
       <c r="R6" s="0" t="str">
         <f aca="false">IF(B6="","",Q6&amp;"#"&amp;A6)</f>
-        <v>soporte móvil para coche de pinza para salpicadero | Amplia#46290</v>
+        <v>soporte móvil para coche de pinza | Exacta#46290</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3241,10 +3466,10 @@
         <v>46290</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>47</v>
@@ -3253,7 +3478,7 @@
         <v>95</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="G7" s="34" t="n">
         <v>0</v>
@@ -3306,7 +3531,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>47</v>
@@ -3377,7 +3602,7 @@
         <v>99</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G9" s="34" t="n">
         <v>0</v>
@@ -3563,7 +3788,7 @@
         <v>105</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="G12" s="34" t="n">
         <v>0</v>
@@ -3601,11 +3826,11 @@
       </c>
       <c r="Q12" s="4" t="str">
         <f aca="false">IF(B12="","",B12&amp;" | "&amp;C12)</f>
-        <v>soporte teléfono coche pinza para salpicadero | Frase</v>
+        <v>soporte móvil coche pinza ajustable | Frase</v>
       </c>
       <c r="R12" s="0" t="str">
         <f aca="false">IF(B12="","",Q12&amp;"#"&amp;A12)</f>
-        <v>soporte teléfono coche pinza para salpicadero | Frase#46290</v>
+        <v>soporte móvil coche pinza ajustable | Frase#46290</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18722,7 +18947,7 @@
         <v>142</v>
       </c>
       <c r="J5" s="40" t="n">
-        <v>0.165</v>
+        <v>0.1891</v>
       </c>
       <c r="K5" s="37" t="s">
         <v>143</v>
@@ -18790,20 +19015,20 @@
         <v>90</v>
       </c>
       <c r="F6" s="39" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="39" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="40" t="n">
         <f aca="false">IF(OR(F6="",G6="",F6=0),"",G6/F6-1)</f>
-        <v>0.254901960784314</v>
+        <v>0</v>
       </c>
       <c r="I6" s="18" t="s">
         <v>144</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>0.2752</v>
+        <v>0.3003</v>
       </c>
       <c r="K6" s="37" t="s">
         <v>143</v>
@@ -18871,10 +19096,10 @@
         <v>93</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="H7" s="40" t="n">
         <f aca="false">IF(OR(F7="",G7="",F7=0),"",G7/F7-1)</f>
@@ -18884,7 +19109,7 @@
         <v>145</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>0.3003</v>
+        <v>0.309</v>
       </c>
       <c r="K7" s="37" t="s">
         <v>143</v>
@@ -18946,26 +19171,26 @@
         <v>141</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F8" s="39" t="n">
         <v>0.41</v>
       </c>
       <c r="G8" s="39" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H8" s="40" t="n">
         <f aca="false">IF(OR(F8="",G8="",F8=0),"",G8/F8-1)</f>
-        <v>-0.0975609756097561</v>
+        <v>0</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>146</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.3647</v>
+        <v>0.316</v>
       </c>
       <c r="K8" s="37" t="s">
         <v>143</v>
@@ -19030,7 +19255,7 @@
         <v>85</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F9" s="39" t="n">
         <v>0.55</v>
@@ -19115,7 +19340,7 @@
       </c>
       <c r="F10" s="39"/>
       <c r="G10" s="39" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="H10" s="40" t="str">
         <f aca="false">IF(OR(F10="",G10="",F10=0),"",G10/F10-1)</f>
@@ -19355,7 +19580,7 @@
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="39" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H13" s="40" t="str">
         <f aca="false">IF(OR(F13="",G13="",F13=0),"",G13/F13-1)</f>
@@ -23189,7 +23414,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P165"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -23268,44 +23493,44 @@
         <v>227</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0.62</v>
+        <v>0.2</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G4" s="23" t="n">
         <f aca="false">IFERROR(F4/E4,0)</f>
-        <v>0.119402985074627</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>10.78</v>
+        <v>1.69</v>
       </c>
       <c r="I4" s="7" t="n">
         <f aca="false">IFERROR(H4/F4,0)</f>
-        <v>0.449166666666667</v>
+        <v>0.281666666666667</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>65.35</v>
+        <v>10.39</v>
       </c>
       <c r="L4" s="23" t="n">
         <f aca="false">IFERROR(H4/K4,0)</f>
-        <v>0.16495791889824</v>
+        <v>0.162656400384986</v>
       </c>
       <c r="M4" s="24" t="n">
         <f aca="false">IFERROR(K4/H4,0)</f>
-        <v>6.06215213358071</v>
+        <v>6.14792899408284</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>228</v>
@@ -23322,47 +23547,47 @@
         <v>227</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>652</v>
+        <v>201</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G5" s="23" t="n">
         <f aca="false">IFERROR(F5/E5,0)</f>
-        <v>0.0184049079754601</v>
+        <v>0.119402985074627</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>6.6</v>
+        <v>10.78</v>
       </c>
       <c r="I5" s="7" t="n">
         <f aca="false">IFERROR(H5/F5,0)</f>
-        <v>0.55</v>
+        <v>0.449166666666667</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>23.98</v>
+        <v>65.35</v>
       </c>
       <c r="L5" s="23" t="n">
         <f aca="false">IFERROR(H5/K5,0)</f>
-        <v>0.275229357798165</v>
+        <v>0.16495791889824</v>
       </c>
       <c r="M5" s="24" t="n">
         <f aca="false">IFERROR(K5/H5,0)</f>
-        <v>3.63333333333333</v>
+        <v>6.06215213358071</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O5" s="12" t="s">
         <v>229</v>
@@ -23382,41 +23607,41 @@
         <v>93</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>75</v>
+        <v>652</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6" s="23" t="n">
         <f aca="false">IFERROR(F6/E6,0)</f>
-        <v>0.12</v>
+        <v>0.0184049079754601</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>3.12</v>
+        <v>6.6</v>
       </c>
       <c r="I6" s="7" t="n">
         <f aca="false">IFERROR(H6/F6,0)</f>
-        <v>0.346666666666667</v>
+        <v>0.55</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>10.39</v>
+        <v>23.98</v>
       </c>
       <c r="L6" s="23" t="n">
         <f aca="false">IFERROR(H6/K6,0)</f>
-        <v>0.300288739172281</v>
+        <v>0.275229357798165</v>
       </c>
       <c r="M6" s="24" t="n">
         <f aca="false">IFERROR(K6/H6,0)</f>
-        <v>3.33012820512821</v>
+        <v>3.63333333333333</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O6" s="12" t="s">
         <v>229</v>
@@ -23433,44 +23658,44 @@
         <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>1497</v>
+        <v>75</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G7" s="23" t="n">
         <f aca="false">IFERROR(F7/E7,0)</f>
-        <v>0.0207080828323313</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>11.95</v>
+        <v>3.12</v>
       </c>
       <c r="I7" s="7" t="n">
         <f aca="false">IFERROR(H7/F7,0)</f>
-        <v>0.385483870967742</v>
+        <v>0.346666666666667</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>32.77</v>
+        <v>10.39</v>
       </c>
       <c r="L7" s="23" t="n">
         <f aca="false">IFERROR(H7/K7,0)</f>
-        <v>0.364662801342691</v>
+        <v>0.300288739172281</v>
       </c>
       <c r="M7" s="24" t="n">
         <f aca="false">IFERROR(K7/H7,0)</f>
-        <v>2.74225941422594</v>
+        <v>3.33012820512821</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O7" s="12" t="s">
         <v>229</v>
@@ -23484,47 +23709,47 @@
         <v>227</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>2929</v>
+        <v>1497</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G8" s="23" t="n">
         <f aca="false">IFERROR(F8/E8,0)</f>
-        <v>0.00614544213041994</v>
+        <v>0.0207080828323313</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>10.83</v>
+        <v>11.95</v>
       </c>
       <c r="I8" s="7" t="n">
         <f aca="false">IFERROR(H8/F8,0)</f>
-        <v>0.601666666666667</v>
+        <v>0.385483870967742</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>22.78</v>
+        <v>32.77</v>
       </c>
       <c r="L8" s="23" t="n">
         <f aca="false">IFERROR(H8/K8,0)</f>
-        <v>0.475417032484636</v>
+        <v>0.364662801342691</v>
       </c>
       <c r="M8" s="24" t="n">
         <f aca="false">IFERROR(K8/H8,0)</f>
-        <v>2.10341643582641</v>
+        <v>2.74225941422594</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>229</v>
@@ -23537,54 +23762,54 @@
       <c r="A9" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>89</v>
+      <c r="B9" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>22090</v>
+        <v>2929</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>205</v>
+        <v>18</v>
       </c>
       <c r="G9" s="23" t="n">
         <f aca="false">IFERROR(F9/E9,0)</f>
-        <v>0.00928021729289271</v>
+        <v>0.00614544213041994</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>109.41</v>
+        <v>10.83</v>
       </c>
       <c r="I9" s="7" t="n">
         <f aca="false">IFERROR(H9/F9,0)</f>
-        <v>0.533707317073171</v>
+        <v>0.601666666666667</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>224.64</v>
+        <v>22.78</v>
       </c>
       <c r="L9" s="23" t="n">
         <f aca="false">IFERROR(H9/K9,0)</f>
-        <v>0.48704594017094</v>
+        <v>0.475417032484636</v>
       </c>
       <c r="M9" s="24" t="n">
         <f aca="false">IFERROR(K9/H9,0)</f>
-        <v>2.05319440636139</v>
+        <v>2.10341643582641</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="O9" s="4" t="s">
         <v>231</v>
       </c>
+      <c r="O9" s="12" t="s">
+        <v>229</v>
+      </c>
       <c r="P9" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23592,53 +23817,53 @@
         <v>227</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>233</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>5975</v>
+        <v>22090</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="G10" s="23" t="n">
         <f aca="false">IFERROR(F10/E10,0)</f>
-        <v>0.00870292887029289</v>
+        <v>0.00928021729289271</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>39.56</v>
+        <v>109.41</v>
       </c>
       <c r="I10" s="7" t="n">
         <f aca="false">IFERROR(H10/F10,0)</f>
-        <v>0.760769230769231</v>
+        <v>0.533707317073171</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>13.5</v>
+        <v>224.64</v>
       </c>
       <c r="L10" s="23" t="n">
         <f aca="false">IFERROR(H10/K10,0)</f>
-        <v>2.93037037037037</v>
+        <v>0.48704594017094</v>
       </c>
       <c r="M10" s="24" t="n">
         <f aca="false">IFERROR(K10/H10,0)</f>
-        <v>0.341253791708797</v>
+        <v>2.05319440636139</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23646,50 +23871,50 @@
         <v>227</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>85</v>
+        <v>234</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>208</v>
+        <v>642</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G11" s="23" t="n">
         <f aca="false">IFERROR(F11/E11,0)</f>
-        <v>0.0192307692307692</v>
+        <v>0.0373831775700935</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.83</v>
+        <v>23.16</v>
       </c>
       <c r="I11" s="7" t="n">
         <f aca="false">IFERROR(H11/F11,0)</f>
-        <v>0.4575</v>
+        <v>0.965</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0</v>
+        <v>11.99</v>
       </c>
       <c r="L11" s="23" t="n">
         <f aca="false">IFERROR(H11/K11,0)</f>
-        <v>0</v>
+        <v>1.93160967472894</v>
       </c>
       <c r="M11" s="24" t="n">
         <f aca="false">IFERROR(K11/H11,0)</f>
-        <v>0</v>
+        <v>0.517702936096719</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>236</v>
@@ -23703,50 +23928,50 @@
         <v>237</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>89</v>
+        <v>5975</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="G12" s="23" t="n">
         <f aca="false">IFERROR(F12/E12,0)</f>
-        <v>0.0337078651685393</v>
+        <v>0.00870292887029289</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.91</v>
+        <v>39.56</v>
       </c>
       <c r="I12" s="7" t="n">
         <f aca="false">IFERROR(H12/F12,0)</f>
-        <v>0.303333333333333</v>
+        <v>0.760769230769231</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="L12" s="23" t="n">
         <f aca="false">IFERROR(H12/K12,0)</f>
-        <v>0</v>
+        <v>2.93037037037037</v>
       </c>
       <c r="M12" s="24" t="n">
         <f aca="false">IFERROR(K12/H12,0)</f>
-        <v>0</v>
+        <v>0.341253791708797</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23754,30 +23979,30 @@
         <v>227</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>253</v>
+        <v>1782</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G13" s="23" t="n">
         <f aca="false">IFERROR(F13/E13,0)</f>
-        <v>0.0158102766798419</v>
+        <v>0.0112233445566779</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1.87</v>
+        <v>19.03</v>
       </c>
       <c r="I13" s="7" t="n">
         <f aca="false">IFERROR(H13/F13,0)</f>
-        <v>0.4675</v>
+        <v>0.9515</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>0</v>
@@ -23794,13 +24019,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23808,30 +24033,30 @@
         <v>227</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.56</v>
+        <v>1.26</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>4</v>
+        <v>270</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G14" s="23" t="n">
         <f aca="false">IFERROR(F14/E14,0)</f>
-        <v>0.5</v>
+        <v>0.0259259259259259</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1.01</v>
+        <v>7.97</v>
       </c>
       <c r="I14" s="7" t="n">
         <f aca="false">IFERROR(H14/F14,0)</f>
-        <v>0.505</v>
+        <v>1.13857142857143</v>
       </c>
       <c r="J14" s="22" t="n">
         <v>0</v>
@@ -23848,13 +24073,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23862,30 +24087,30 @@
         <v>227</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>92</v>
+        <v>244</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>1</v>
+        <v>454</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="23" t="n">
         <f aca="false">IFERROR(F15/E15,0)</f>
-        <v>0</v>
+        <v>0.00881057268722467</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="I15" s="7" t="n">
         <f aca="false">IFERROR(H15/F15,0)</f>
-        <v>0</v>
+        <v>1.3025</v>
       </c>
       <c r="J15" s="22" t="n">
         <v>0</v>
@@ -23902,13 +24127,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23916,30 +24141,30 @@
         <v>227</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" s="23" t="n">
         <f aca="false">IFERROR(F16/E16,0)</f>
-        <v>0</v>
+        <v>0.036036036036036</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="I16" s="7" t="n">
         <f aca="false">IFERROR(H16/F16,0)</f>
-        <v>0</v>
+        <v>0.8025</v>
       </c>
       <c r="J16" s="22" t="n">
         <v>0</v>
@@ -23956,13 +24181,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23970,30 +24195,30 @@
         <v>227</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G17" s="23" t="n">
         <f aca="false">IFERROR(F17/E17,0)</f>
-        <v>0</v>
+        <v>0.0133333333333333</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I17" s="7" t="n">
         <f aca="false">IFERROR(H17/F17,0)</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J17" s="22" t="n">
         <v>0</v>
@@ -24010,13 +24235,13 @@
         <v>0</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24024,30 +24249,30 @@
         <v>227</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.56</v>
+        <v>0.34</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="23" t="n">
         <f aca="false">IFERROR(F18/E18,0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="I18" s="7" t="n">
         <f aca="false">IFERROR(H18/F18,0)</f>
-        <v>0</v>
+        <v>0.593333333333333</v>
       </c>
       <c r="J18" s="22" t="n">
         <v>0</v>
@@ -24064,13 +24289,13 @@
         <v>0</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24078,30 +24303,30 @@
         <v>227</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.56</v>
+        <v>0.47</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="23" t="n">
         <f aca="false">IFERROR(F19/E19,0)</f>
-        <v>0</v>
+        <v>0.0277777777777778</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="I19" s="7" t="n">
         <f aca="false">IFERROR(H19/F19,0)</f>
-        <v>0</v>
+        <v>0.805</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>0</v>
@@ -24118,44 +24343,44 @@
         <v>0</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>243</v>
+      <c r="B20" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.56</v>
+        <v>0.7</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" s="23" t="n">
         <f aca="false">IFERROR(F20/E20,0)</f>
-        <v>0</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="I20" s="7" t="n">
         <f aca="false">IFERROR(H20/F20,0)</f>
-        <v>0</v>
+        <v>0.526666666666667</v>
       </c>
       <c r="J20" s="22" t="n">
         <v>0</v>
@@ -24172,13 +24397,13 @@
         <v>0</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24186,30 +24411,30 @@
         <v>227</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.56</v>
+        <v>0.76</v>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="23" t="n">
         <f aca="false">IFERROR(F21/E21,0)</f>
-        <v>0</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="I21" s="7" t="n">
         <f aca="false">IFERROR(H21/F21,0)</f>
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="J21" s="22" t="n">
         <v>0</v>
@@ -24226,47 +24451,7122 @@
         <v>0</v>
       </c>
       <c r="N21" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>88</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <f aca="false">IFERROR(F22/E22,0)</f>
+        <v>0.0227272727272727</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <f aca="false">IFERROR(H22/F22,0)</f>
+        <v>0.735</v>
+      </c>
+      <c r="J22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="23" t="n">
+        <f aca="false">IFERROR(H22/K22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="24" t="n">
+        <f aca="false">IFERROR(K22/H22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <f aca="false">IFERROR(F23/E23,0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <f aca="false">IFERROR(H23/F23,0)</f>
+        <v>0.715</v>
+      </c>
+      <c r="J23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="23" t="n">
+        <f aca="false">IFERROR(H23/K23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="24" t="n">
+        <f aca="false">IFERROR(K23/H23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="23" t="n">
+        <f aca="false">IFERROR(F24/E24,0)</f>
+        <v>0.0111111111111111</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <f aca="false">IFERROR(H24/F24,0)</f>
+        <v>1.31</v>
+      </c>
+      <c r="J24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="23" t="n">
+        <f aca="false">IFERROR(H24/K24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="24" t="n">
+        <f aca="false">IFERROR(K24/H24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="23" t="n">
+        <f aca="false">IFERROR(F25/E25,0)</f>
+        <v>0.0909090909090909</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <f aca="false">IFERROR(H25/F25,0)</f>
+        <v>1.26</v>
+      </c>
+      <c r="J25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <f aca="false">IFERROR(H25/K25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="24" t="n">
+        <f aca="false">IFERROR(K25/H25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>943</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="23" t="n">
+        <f aca="false">IFERROR(F26/E26,0)</f>
+        <v>0.00212089077412513</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <f aca="false">IFERROR(H26/F26,0)</f>
+        <v>0.605</v>
+      </c>
+      <c r="J26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="23" t="n">
+        <f aca="false">IFERROR(H26/K26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="24" t="n">
+        <f aca="false">IFERROR(K26/H26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="23" t="n">
+        <f aca="false">IFERROR(F27/E27,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <f aca="false">IFERROR(H27/F27,0)</f>
+        <v>1.16</v>
+      </c>
+      <c r="J27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="23" t="n">
+        <f aca="false">IFERROR(H27/K27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="24" t="n">
+        <f aca="false">IFERROR(K27/H27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>377</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <f aca="false">IFERROR(F28/E28,0)</f>
+        <v>0.0026525198938992</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <f aca="false">IFERROR(H28/F28,0)</f>
+        <v>1.15</v>
+      </c>
+      <c r="J28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="23" t="n">
+        <f aca="false">IFERROR(H28/K28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="24" t="n">
+        <f aca="false">IFERROR(K28/H28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <f aca="false">IFERROR(F29/E29,0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <f aca="false">IFERROR(H29/F29,0)</f>
+        <v>0.505</v>
+      </c>
+      <c r="J29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="23" t="n">
+        <f aca="false">IFERROR(H29/K29,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="24" t="n">
+        <f aca="false">IFERROR(K29/H29,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <f aca="false">IFERROR(F30/E30,0)</f>
+        <v>0.0454545454545455</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <f aca="false">IFERROR(H30/F30,0)</f>
+        <v>0.44</v>
+      </c>
+      <c r="J30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="23" t="n">
+        <f aca="false">IFERROR(H30/K30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <f aca="false">IFERROR(K30/H30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>89</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <f aca="false">IFERROR(F31/E31,0)</f>
+        <v>0.0224719101123596</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <f aca="false">IFERROR(H31/F31,0)</f>
+        <v>0.405</v>
+      </c>
+      <c r="J31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <f aca="false">IFERROR(H31/K31,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="24" t="n">
+        <f aca="false">IFERROR(K31/H31,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="23" t="n">
+        <f aca="false">IFERROR(F32/E32,0)</f>
+        <v>0.0263157894736842</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <f aca="false">IFERROR(H32/F32,0)</f>
+        <v>0.72</v>
+      </c>
+      <c r="J32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="23" t="n">
+        <f aca="false">IFERROR(H32/K32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="24" t="n">
+        <f aca="false">IFERROR(K32/H32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="C33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <f aca="false">IFERROR(F33/E33,0)</f>
+        <v>0.027027027027027</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <f aca="false">IFERROR(H33/F33,0)</f>
+        <v>0.26</v>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="23" t="n">
+        <f aca="false">IFERROR(H33/K33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="24" t="n">
+        <f aca="false">IFERROR(K33/H33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="23" t="n">
+        <f aca="false">IFERROR(F34/E34,0)</f>
+        <v>0.0769230769230769</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <f aca="false">IFERROR(H34/F34,0)</f>
+        <v>0.21</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="23" t="n">
+        <f aca="false">IFERROR(H34/K34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="24" t="n">
+        <f aca="false">IFERROR(K34/H34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>253</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="23" t="n">
+        <f aca="false">IFERROR(F35/E35,0)</f>
+        <v>0.0158102766798419</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <f aca="false">IFERROR(H35/F35,0)</f>
+        <v>0.4675</v>
+      </c>
+      <c r="J35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="23" t="n">
+        <f aca="false">IFERROR(H35/K35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="24" t="n">
+        <f aca="false">IFERROR(K35/H35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="O35" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E36" s="22" t="n">
+        <v>208</v>
+      </c>
+      <c r="F36" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="23" t="n">
+        <f aca="false">IFERROR(F36/E36,0)</f>
+        <v>0.0192307692307692</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <f aca="false">IFERROR(H36/F36,0)</f>
+        <v>0.4575</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="23" t="n">
+        <f aca="false">IFERROR(H36/K36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="24" t="n">
+        <f aca="false">IFERROR(K36/H36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>89</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="23" t="n">
+        <f aca="false">IFERROR(F37/E37,0)</f>
+        <v>0.0337078651685393</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <f aca="false">IFERROR(H37/F37,0)</f>
+        <v>0.303333333333333</v>
+      </c>
+      <c r="J37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="23" t="n">
+        <f aca="false">IFERROR(H37/K37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M37" s="24" t="n">
+        <f aca="false">IFERROR(K37/H37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <f aca="false">IFERROR(F38/E38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <f aca="false">IFERROR(H38/F38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="23" t="n">
+        <f aca="false">IFERROR(H38/K38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="24" t="n">
+        <f aca="false">IFERROR(K38/H38,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="23" t="n">
+        <f aca="false">IFERROR(F39/E39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <f aca="false">IFERROR(H39/F39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="23" t="n">
+        <f aca="false">IFERROR(H39/K39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="24" t="n">
+        <f aca="false">IFERROR(K39/H39,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <f aca="false">IFERROR(F40/E40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <f aca="false">IFERROR(H40/F40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="23" t="n">
+        <f aca="false">IFERROR(H40/K40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="24" t="n">
+        <f aca="false">IFERROR(K40/H40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <f aca="false">IFERROR(F41/E41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <f aca="false">IFERROR(H41/F41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="23" t="n">
+        <f aca="false">IFERROR(H41/K41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="24" t="n">
+        <f aca="false">IFERROR(K41/H41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <f aca="false">IFERROR(F42/E42,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <f aca="false">IFERROR(H42/F42,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="23" t="n">
+        <f aca="false">IFERROR(H42/K42,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="24" t="n">
+        <f aca="false">IFERROR(K42/H42,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="C43" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <f aca="false">IFERROR(F43/E43,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <f aca="false">IFERROR(H43/F43,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="23" t="n">
+        <f aca="false">IFERROR(H43/K43,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="24" t="n">
+        <f aca="false">IFERROR(K43/H43,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <f aca="false">IFERROR(F44/E44,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <f aca="false">IFERROR(H44/F44,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="23" t="n">
+        <f aca="false">IFERROR(H44/K44,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="24" t="n">
+        <f aca="false">IFERROR(K44/H44,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <f aca="false">IFERROR(F45/E45,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <f aca="false">IFERROR(H45/F45,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="23" t="n">
+        <f aca="false">IFERROR(H45/K45,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="24" t="n">
+        <f aca="false">IFERROR(K45/H45,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <f aca="false">IFERROR(F46/E46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <f aca="false">IFERROR(H46/F46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="23" t="n">
+        <f aca="false">IFERROR(H46/K46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="24" t="n">
+        <f aca="false">IFERROR(K46/H46,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <f aca="false">IFERROR(F47/E47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <f aca="false">IFERROR(H47/F47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="23" t="n">
+        <f aca="false">IFERROR(H47/K47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="24" t="n">
+        <f aca="false">IFERROR(K47/H47,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <f aca="false">IFERROR(F48/E48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <f aca="false">IFERROR(H48/F48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="23" t="n">
+        <f aca="false">IFERROR(H48/K48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="24" t="n">
+        <f aca="false">IFERROR(K48/H48,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <f aca="false">IFERROR(F49/E49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <f aca="false">IFERROR(H49/F49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="23" t="n">
+        <f aca="false">IFERROR(H49/K49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="24" t="n">
+        <f aca="false">IFERROR(K49/H49,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <f aca="false">IFERROR(F50/E50,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <f aca="false">IFERROR(H50/F50,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="23" t="n">
+        <f aca="false">IFERROR(H50/K50,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="24" t="n">
+        <f aca="false">IFERROR(K50/H50,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="23" t="n">
+        <f aca="false">IFERROR(F51/E51,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <f aca="false">IFERROR(H51/F51,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="23" t="n">
+        <f aca="false">IFERROR(H51/K51,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="24" t="n">
+        <f aca="false">IFERROR(K51/H51,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <f aca="false">IFERROR(F52/E52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <f aca="false">IFERROR(H52/F52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="23" t="n">
+        <f aca="false">IFERROR(H52/K52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="24" t="n">
+        <f aca="false">IFERROR(K52/H52,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <f aca="false">IFERROR(F53/E53,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <f aca="false">IFERROR(H53/F53,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="23" t="n">
+        <f aca="false">IFERROR(H53/K53,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="24" t="n">
+        <f aca="false">IFERROR(K53/H53,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <f aca="false">IFERROR(F54/E54,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <f aca="false">IFERROR(H54/F54,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="23" t="n">
+        <f aca="false">IFERROR(H54/K54,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="24" t="n">
+        <f aca="false">IFERROR(K54/H54,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="23" t="n">
+        <f aca="false">IFERROR(F55/E55,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <f aca="false">IFERROR(H55/F55,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="23" t="n">
+        <f aca="false">IFERROR(H55/K55,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="24" t="n">
+        <f aca="false">IFERROR(K55/H55,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="23" t="n">
+        <f aca="false">IFERROR(F56/E56,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <f aca="false">IFERROR(H56/F56,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="23" t="n">
+        <f aca="false">IFERROR(H56/K56,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="24" t="n">
+        <f aca="false">IFERROR(K56/H56,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <f aca="false">IFERROR(F57/E57,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <f aca="false">IFERROR(H57/F57,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="23" t="n">
+        <f aca="false">IFERROR(H57/K57,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="24" t="n">
+        <f aca="false">IFERROR(K57/H57,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <f aca="false">IFERROR(F58/E58,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <f aca="false">IFERROR(H58/F58,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="23" t="n">
+        <f aca="false">IFERROR(H58/K58,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="24" t="n">
+        <f aca="false">IFERROR(K58/H58,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="23" t="n">
+        <f aca="false">IFERROR(F59/E59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <f aca="false">IFERROR(H59/F59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="23" t="n">
+        <f aca="false">IFERROR(H59/K59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="24" t="n">
+        <f aca="false">IFERROR(K59/H59,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <f aca="false">IFERROR(F60/E60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <f aca="false">IFERROR(H60/F60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="23" t="n">
+        <f aca="false">IFERROR(H60/K60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="24" t="n">
+        <f aca="false">IFERROR(K60/H60,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E61" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="23" t="n">
+        <f aca="false">IFERROR(F61/E61,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <f aca="false">IFERROR(H61/F61,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="23" t="n">
+        <f aca="false">IFERROR(H61/K61,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="24" t="n">
+        <f aca="false">IFERROR(K61/H61,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E62" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="23" t="n">
+        <f aca="false">IFERROR(F62/E62,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <f aca="false">IFERROR(H62/F62,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="23" t="n">
+        <f aca="false">IFERROR(H62/K62,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="24" t="n">
+        <f aca="false">IFERROR(K62/H62,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E63" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="23" t="n">
+        <f aca="false">IFERROR(F63/E63,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <f aca="false">IFERROR(H63/F63,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="23" t="n">
+        <f aca="false">IFERROR(H63/K63,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="24" t="n">
+        <f aca="false">IFERROR(K63/H63,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E64" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="23" t="n">
+        <f aca="false">IFERROR(F64/E64,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <f aca="false">IFERROR(H64/F64,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="23" t="n">
+        <f aca="false">IFERROR(H64/K64,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="24" t="n">
+        <f aca="false">IFERROR(K64/H64,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E65" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="23" t="n">
+        <f aca="false">IFERROR(F65/E65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <f aca="false">IFERROR(H65/F65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="23" t="n">
+        <f aca="false">IFERROR(H65/K65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="24" t="n">
+        <f aca="false">IFERROR(K65/H65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E66" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="23" t="n">
+        <f aca="false">IFERROR(F66/E66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <f aca="false">IFERROR(H66/F66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="23" t="n">
+        <f aca="false">IFERROR(H66/K66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="24" t="n">
+        <f aca="false">IFERROR(K66/H66,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E67" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="23" t="n">
+        <f aca="false">IFERROR(F67/E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <f aca="false">IFERROR(H67/F67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="23" t="n">
+        <f aca="false">IFERROR(H67/K67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="24" t="n">
+        <f aca="false">IFERROR(K67/H67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="E68" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="23" t="n">
+        <f aca="false">IFERROR(F68/E68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <f aca="false">IFERROR(H68/F68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="23" t="n">
+        <f aca="false">IFERROR(H68/K68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="24" t="n">
+        <f aca="false">IFERROR(K68/H68,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E69" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="23" t="n">
+        <f aca="false">IFERROR(F69/E69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <f aca="false">IFERROR(H69/F69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="23" t="n">
+        <f aca="false">IFERROR(H69/K69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="24" t="n">
+        <f aca="false">IFERROR(K69/H69,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E70" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="23" t="n">
+        <f aca="false">IFERROR(F70/E70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <f aca="false">IFERROR(H70/F70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="23" t="n">
+        <f aca="false">IFERROR(H70/K70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="24" t="n">
+        <f aca="false">IFERROR(K70/H70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E71" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="23" t="n">
+        <f aca="false">IFERROR(F71/E71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <f aca="false">IFERROR(H71/F71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="23" t="n">
+        <f aca="false">IFERROR(H71/K71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="24" t="n">
+        <f aca="false">IFERROR(K71/H71,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E72" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="23" t="n">
+        <f aca="false">IFERROR(F72/E72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <f aca="false">IFERROR(H72/F72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="23" t="n">
+        <f aca="false">IFERROR(H72/K72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="24" t="n">
+        <f aca="false">IFERROR(K72/H72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E73" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="23" t="n">
+        <f aca="false">IFERROR(F73/E73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <f aca="false">IFERROR(H73/F73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="23" t="n">
+        <f aca="false">IFERROR(H73/K73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M73" s="24" t="n">
+        <f aca="false">IFERROR(K73/H73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="23" t="n">
+        <f aca="false">IFERROR(F74/E74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <f aca="false">IFERROR(H74/F74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="23" t="n">
+        <f aca="false">IFERROR(H74/K74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M74" s="24" t="n">
+        <f aca="false">IFERROR(K74/H74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="23" t="n">
+        <f aca="false">IFERROR(F75/E75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <f aca="false">IFERROR(H75/F75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J75" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="23" t="n">
+        <f aca="false">IFERROR(H75/K75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M75" s="24" t="n">
+        <f aca="false">IFERROR(K75/H75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="23" t="n">
+        <f aca="false">IFERROR(F76/E76,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <f aca="false">IFERROR(H76/F76,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="23" t="n">
+        <f aca="false">IFERROR(H76/K76,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="24" t="n">
+        <f aca="false">IFERROR(K76/H76,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="E77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="23" t="n">
+        <f aca="false">IFERROR(F77/E77,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <f aca="false">IFERROR(H77/F77,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="23" t="n">
+        <f aca="false">IFERROR(H77/K77,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="24" t="n">
+        <f aca="false">IFERROR(K77/H77,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E78" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="23" t="n">
+        <f aca="false">IFERROR(F78/E78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <f aca="false">IFERROR(H78/F78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J78" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="23" t="n">
+        <f aca="false">IFERROR(H78/K78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M78" s="24" t="n">
+        <f aca="false">IFERROR(K78/H78,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E79" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="23" t="n">
+        <f aca="false">IFERROR(F79/E79,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <f aca="false">IFERROR(H79/F79,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J79" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="23" t="n">
+        <f aca="false">IFERROR(H79/K79,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M79" s="24" t="n">
+        <f aca="false">IFERROR(K79/H79,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="23" t="n">
+        <f aca="false">IFERROR(F80/E80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <f aca="false">IFERROR(H80/F80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="23" t="n">
+        <f aca="false">IFERROR(H80/K80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M80" s="24" t="n">
+        <f aca="false">IFERROR(K80/H80,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E81" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="23" t="n">
+        <f aca="false">IFERROR(F81/E81,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <f aca="false">IFERROR(H81/F81,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J81" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="23" t="n">
+        <f aca="false">IFERROR(H81/K81,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M81" s="24" t="n">
+        <f aca="false">IFERROR(K81/H81,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="23" t="n">
+        <f aca="false">IFERROR(F82/E82,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <f aca="false">IFERROR(H82/F82,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J82" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="23" t="n">
+        <f aca="false">IFERROR(H82/K82,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="24" t="n">
+        <f aca="false">IFERROR(K82/H82,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="23" t="n">
+        <f aca="false">IFERROR(F83/E83,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <f aca="false">IFERROR(H83/F83,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="23" t="n">
+        <f aca="false">IFERROR(H83/K83,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="24" t="n">
+        <f aca="false">IFERROR(K83/H83,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="23" t="n">
+        <f aca="false">IFERROR(F84/E84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <f aca="false">IFERROR(H84/F84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="23" t="n">
+        <f aca="false">IFERROR(H84/K84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="24" t="n">
+        <f aca="false">IFERROR(K84/H84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="23" t="n">
+        <f aca="false">IFERROR(F85/E85,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <f aca="false">IFERROR(H85/F85,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J85" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="23" t="n">
+        <f aca="false">IFERROR(H85/K85,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="24" t="n">
+        <f aca="false">IFERROR(K85/H85,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="23" t="n">
+        <f aca="false">IFERROR(F86/E86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <f aca="false">IFERROR(H86/F86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J86" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="23" t="n">
+        <f aca="false">IFERROR(H86/K86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M86" s="24" t="n">
+        <f aca="false">IFERROR(K86/H86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="23" t="n">
+        <f aca="false">IFERROR(F87/E87,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <f aca="false">IFERROR(H87/F87,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="23" t="n">
+        <f aca="false">IFERROR(H87/K87,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M87" s="24" t="n">
+        <f aca="false">IFERROR(K87/H87,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="23" t="n">
+        <f aca="false">IFERROR(F88/E88,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="7" t="n">
+        <f aca="false">IFERROR(H88/F88,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="23" t="n">
+        <f aca="false">IFERROR(H88/K88,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M88" s="24" t="n">
+        <f aca="false">IFERROR(K88/H88,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="23" t="n">
+        <f aca="false">IFERROR(F89/E89,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="7" t="n">
+        <f aca="false">IFERROR(H89/F89,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="23" t="n">
+        <f aca="false">IFERROR(H89/K89,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M89" s="24" t="n">
+        <f aca="false">IFERROR(K89/H89,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O89" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="23" t="n">
+        <f aca="false">IFERROR(F90/E90,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="7" t="n">
+        <f aca="false">IFERROR(H90/F90,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="23" t="n">
+        <f aca="false">IFERROR(H90/K90,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M90" s="24" t="n">
+        <f aca="false">IFERROR(K90/H90,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="23" t="n">
+        <f aca="false">IFERROR(F91/E91,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <f aca="false">IFERROR(H91/F91,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="23" t="n">
+        <f aca="false">IFERROR(H91/K91,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M91" s="24" t="n">
+        <f aca="false">IFERROR(K91/H91,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="23" t="n">
+        <f aca="false">IFERROR(F92/E92,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <f aca="false">IFERROR(H92/F92,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="23" t="n">
+        <f aca="false">IFERROR(H92/K92,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M92" s="24" t="n">
+        <f aca="false">IFERROR(K92/H92,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P92" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="23" t="n">
+        <f aca="false">IFERROR(F93/E93,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <f aca="false">IFERROR(H93/F93,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="23" t="n">
+        <f aca="false">IFERROR(H93/K93,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M93" s="24" t="n">
+        <f aca="false">IFERROR(K93/H93,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P93" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="23" t="n">
+        <f aca="false">IFERROR(F94/E94,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="7" t="n">
+        <f aca="false">IFERROR(H94/F94,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="23" t="n">
+        <f aca="false">IFERROR(H94/K94,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="24" t="n">
+        <f aca="false">IFERROR(K94/H94,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P94" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="23" t="n">
+        <f aca="false">IFERROR(F95/E95,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <f aca="false">IFERROR(H95/F95,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="23" t="n">
+        <f aca="false">IFERROR(H95/K95,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M95" s="24" t="n">
+        <f aca="false">IFERROR(K95/H95,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B96" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E22" s="47" t="n">
-        <f aca="false">SUM(E4:E21)</f>
-        <v>33975</v>
-      </c>
-      <c r="F22" s="47" t="n">
-        <f aca="false">SUM(F4:F21)</f>
-        <v>364</v>
-      </c>
-      <c r="H22" s="48" t="n">
-        <f aca="false">SUM(H4:H21)</f>
-        <v>197.87</v>
-      </c>
-      <c r="J22" s="47" t="n">
-        <f aca="false">SUM(J4:J21)</f>
-        <v>35</v>
-      </c>
-      <c r="K22" s="48" t="n">
-        <f aca="false">SUM(K4:K21)</f>
-        <v>393.41</v>
-      </c>
-      <c r="L22" s="49" t="n">
-        <f aca="false">IFERROR(H22/K22,0)</f>
-        <v>0.502961287206731</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="2" t="s">
+      <c r="C96" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="23" t="n">
+        <f aca="false">IFERROR(F96/E96,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <f aca="false">IFERROR(H96/F96,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="23" t="n">
+        <f aca="false">IFERROR(H96/K96,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M96" s="24" t="n">
+        <f aca="false">IFERROR(K96/H96,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P96" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="23" t="n">
+        <f aca="false">IFERROR(F97/E97,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <f aca="false">IFERROR(H97/F97,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="23" t="n">
+        <f aca="false">IFERROR(H97/K97,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M97" s="24" t="n">
+        <f aca="false">IFERROR(K97/H97,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N97" s="4" t="s">
         <v>246</v>
+      </c>
+      <c r="O97" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P97" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="23" t="n">
+        <f aca="false">IFERROR(F98/E98,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <f aca="false">IFERROR(H98/F98,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="23" t="n">
+        <f aca="false">IFERROR(H98/K98,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M98" s="24" t="n">
+        <f aca="false">IFERROR(K98/H98,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P98" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="23" t="n">
+        <f aca="false">IFERROR(F99/E99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <f aca="false">IFERROR(H99/F99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="23" t="n">
+        <f aca="false">IFERROR(H99/K99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="24" t="n">
+        <f aca="false">IFERROR(K99/H99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O99" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P99" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="23" t="n">
+        <f aca="false">IFERROR(F100/E100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <f aca="false">IFERROR(H100/F100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="23" t="n">
+        <f aca="false">IFERROR(H100/K100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M100" s="24" t="n">
+        <f aca="false">IFERROR(K100/H100,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P100" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="23" t="n">
+        <f aca="false">IFERROR(F101/E101,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <f aca="false">IFERROR(H101/F101,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="23" t="n">
+        <f aca="false">IFERROR(H101/K101,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M101" s="24" t="n">
+        <f aca="false">IFERROR(K101/H101,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O101" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P101" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="23" t="n">
+        <f aca="false">IFERROR(F102/E102,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <f aca="false">IFERROR(H102/F102,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="23" t="n">
+        <f aca="false">IFERROR(H102/K102,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M102" s="24" t="n">
+        <f aca="false">IFERROR(K102/H102,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O102" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P102" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="23" t="n">
+        <f aca="false">IFERROR(F103/E103,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <f aca="false">IFERROR(H103/F103,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="23" t="n">
+        <f aca="false">IFERROR(H103/K103,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="24" t="n">
+        <f aca="false">IFERROR(K103/H103,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="23" t="n">
+        <f aca="false">IFERROR(F104/E104,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <f aca="false">IFERROR(H104/F104,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="23" t="n">
+        <f aca="false">IFERROR(H104/K104,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="24" t="n">
+        <f aca="false">IFERROR(K104/H104,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O104" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P104" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="23" t="n">
+        <f aca="false">IFERROR(F105/E105,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <f aca="false">IFERROR(H105/F105,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="23" t="n">
+        <f aca="false">IFERROR(H105/K105,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M105" s="24" t="n">
+        <f aca="false">IFERROR(K105/H105,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P105" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="23" t="n">
+        <f aca="false">IFERROR(F106/E106,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <f aca="false">IFERROR(H106/F106,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="23" t="n">
+        <f aca="false">IFERROR(H106/K106,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M106" s="24" t="n">
+        <f aca="false">IFERROR(K106/H106,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O106" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="23" t="n">
+        <f aca="false">IFERROR(F107/E107,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="7" t="n">
+        <f aca="false">IFERROR(H107/F107,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="23" t="n">
+        <f aca="false">IFERROR(H107/K107,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M107" s="24" t="n">
+        <f aca="false">IFERROR(K107/H107,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O107" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P107" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="23" t="n">
+        <f aca="false">IFERROR(F108/E108,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="7" t="n">
+        <f aca="false">IFERROR(H108/F108,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J108" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="23" t="n">
+        <f aca="false">IFERROR(H108/K108,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M108" s="24" t="n">
+        <f aca="false">IFERROR(K108/H108,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N108" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O108" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P108" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="23" t="n">
+        <f aca="false">IFERROR(F109/E109,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <f aca="false">IFERROR(H109/F109,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="23" t="n">
+        <f aca="false">IFERROR(H109/K109,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="24" t="n">
+        <f aca="false">IFERROR(K109/H109,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N109" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O109" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P109" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="23" t="n">
+        <f aca="false">IFERROR(F110/E110,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="7" t="n">
+        <f aca="false">IFERROR(H110/F110,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="23" t="n">
+        <f aca="false">IFERROR(H110/K110,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M110" s="24" t="n">
+        <f aca="false">IFERROR(K110/H110,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N110" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O110" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P110" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="23" t="n">
+        <f aca="false">IFERROR(F111/E111,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="7" t="n">
+        <f aca="false">IFERROR(H111/F111,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="23" t="n">
+        <f aca="false">IFERROR(H111/K111,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M111" s="24" t="n">
+        <f aca="false">IFERROR(K111/H111,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N111" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O111" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P111" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="23" t="n">
+        <f aca="false">IFERROR(F112/E112,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="7" t="n">
+        <f aca="false">IFERROR(H112/F112,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="23" t="n">
+        <f aca="false">IFERROR(H112/K112,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M112" s="24" t="n">
+        <f aca="false">IFERROR(K112/H112,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N112" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O112" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P112" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="23" t="n">
+        <f aca="false">IFERROR(F113/E113,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <f aca="false">IFERROR(H113/F113,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="23" t="n">
+        <f aca="false">IFERROR(H113/K113,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M113" s="24" t="n">
+        <f aca="false">IFERROR(K113/H113,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N113" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O113" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P113" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="23" t="n">
+        <f aca="false">IFERROR(F114/E114,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="7" t="n">
+        <f aca="false">IFERROR(H114/F114,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="23" t="n">
+        <f aca="false">IFERROR(H114/K114,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M114" s="24" t="n">
+        <f aca="false">IFERROR(K114/H114,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N114" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O114" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P114" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E115" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="23" t="n">
+        <f aca="false">IFERROR(F115/E115,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="7" t="n">
+        <f aca="false">IFERROR(H115/F115,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="23" t="n">
+        <f aca="false">IFERROR(H115/K115,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M115" s="24" t="n">
+        <f aca="false">IFERROR(K115/H115,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N115" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O115" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P115" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="23" t="n">
+        <f aca="false">IFERROR(F116/E116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H116" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="7" t="n">
+        <f aca="false">IFERROR(H116/F116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J116" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="23" t="n">
+        <f aca="false">IFERROR(H116/K116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M116" s="24" t="n">
+        <f aca="false">IFERROR(K116/H116,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O116" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P116" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E117" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="23" t="n">
+        <f aca="false">IFERROR(F117/E117,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="7" t="n">
+        <f aca="false">IFERROR(H117/F117,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J117" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="23" t="n">
+        <f aca="false">IFERROR(H117/K117,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M117" s="24" t="n">
+        <f aca="false">IFERROR(K117/H117,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O117" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P117" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E118" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="23" t="n">
+        <f aca="false">IFERROR(F118/E118,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H118" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="7" t="n">
+        <f aca="false">IFERROR(H118/F118,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="23" t="n">
+        <f aca="false">IFERROR(H118/K118,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M118" s="24" t="n">
+        <f aca="false">IFERROR(K118/H118,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O118" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P118" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="23" t="n">
+        <f aca="false">IFERROR(F119/E119,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="7" t="n">
+        <f aca="false">IFERROR(H119/F119,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="23" t="n">
+        <f aca="false">IFERROR(H119/K119,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M119" s="24" t="n">
+        <f aca="false">IFERROR(K119/H119,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O119" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P119" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="23" t="n">
+        <f aca="false">IFERROR(F120/E120,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H120" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="7" t="n">
+        <f aca="false">IFERROR(H120/F120,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="23" t="n">
+        <f aca="false">IFERROR(H120/K120,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M120" s="24" t="n">
+        <f aca="false">IFERROR(K120/H120,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P120" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="23" t="n">
+        <f aca="false">IFERROR(F121/E121,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="7" t="n">
+        <f aca="false">IFERROR(H121/F121,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="23" t="n">
+        <f aca="false">IFERROR(H121/K121,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M121" s="24" t="n">
+        <f aca="false">IFERROR(K121/H121,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O121" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P121" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="23" t="n">
+        <f aca="false">IFERROR(F122/E122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="7" t="n">
+        <f aca="false">IFERROR(H122/F122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="23" t="n">
+        <f aca="false">IFERROR(H122/K122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M122" s="24" t="n">
+        <f aca="false">IFERROR(K122/H122,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N122" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O122" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P122" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="23" t="n">
+        <f aca="false">IFERROR(F123/E123,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="7" t="n">
+        <f aca="false">IFERROR(H123/F123,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J123" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="23" t="n">
+        <f aca="false">IFERROR(H123/K123,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M123" s="24" t="n">
+        <f aca="false">IFERROR(K123/H123,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N123" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O123" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P123" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="23" t="n">
+        <f aca="false">IFERROR(F124/E124,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="7" t="n">
+        <f aca="false">IFERROR(H124/F124,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J124" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="23" t="n">
+        <f aca="false">IFERROR(H124/K124,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M124" s="24" t="n">
+        <f aca="false">IFERROR(K124/H124,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N124" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O124" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P124" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E125" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="23" t="n">
+        <f aca="false">IFERROR(F125/E125,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="7" t="n">
+        <f aca="false">IFERROR(H125/F125,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J125" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="23" t="n">
+        <f aca="false">IFERROR(H125/K125,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M125" s="24" t="n">
+        <f aca="false">IFERROR(K125/H125,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N125" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O125" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P125" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E126" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="23" t="n">
+        <f aca="false">IFERROR(F126/E126,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="7" t="n">
+        <f aca="false">IFERROR(H126/F126,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J126" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="23" t="n">
+        <f aca="false">IFERROR(H126/K126,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M126" s="24" t="n">
+        <f aca="false">IFERROR(K126/H126,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N126" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O126" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P126" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E127" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="23" t="n">
+        <f aca="false">IFERROR(F127/E127,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="7" t="n">
+        <f aca="false">IFERROR(H127/F127,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J127" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="23" t="n">
+        <f aca="false">IFERROR(H127/K127,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M127" s="24" t="n">
+        <f aca="false">IFERROR(K127/H127,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N127" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O127" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P127" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="23" t="n">
+        <f aca="false">IFERROR(F128/E128,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="7" t="n">
+        <f aca="false">IFERROR(H128/F128,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="23" t="n">
+        <f aca="false">IFERROR(H128/K128,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M128" s="24" t="n">
+        <f aca="false">IFERROR(K128/H128,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N128" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="O128" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P128" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <f aca="false">IFERROR(F129/E129,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="7" t="n">
+        <f aca="false">IFERROR(H129/F129,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J129" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="23" t="n">
+        <f aca="false">IFERROR(H129/K129,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M129" s="24" t="n">
+        <f aca="false">IFERROR(K129/H129,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N129" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O129" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P129" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <f aca="false">IFERROR(F130/E130,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="7" t="n">
+        <f aca="false">IFERROR(H130/F130,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="23" t="n">
+        <f aca="false">IFERROR(H130/K130,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M130" s="24" t="n">
+        <f aca="false">IFERROR(K130/H130,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N130" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O130" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P130" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="23" t="n">
+        <f aca="false">IFERROR(F131/E131,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="7" t="n">
+        <f aca="false">IFERROR(H131/F131,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J131" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="23" t="n">
+        <f aca="false">IFERROR(H131/K131,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M131" s="24" t="n">
+        <f aca="false">IFERROR(K131/H131,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N131" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O131" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P131" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="23" t="n">
+        <f aca="false">IFERROR(F132/E132,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H132" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="7" t="n">
+        <f aca="false">IFERROR(H132/F132,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J132" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="23" t="n">
+        <f aca="false">IFERROR(H132/K132,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M132" s="24" t="n">
+        <f aca="false">IFERROR(K132/H132,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N132" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O132" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P132" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="23" t="n">
+        <f aca="false">IFERROR(F133/E133,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="7" t="n">
+        <f aca="false">IFERROR(H133/F133,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="23" t="n">
+        <f aca="false">IFERROR(H133/K133,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M133" s="24" t="n">
+        <f aca="false">IFERROR(K133/H133,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N133" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O133" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P133" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="23" t="n">
+        <f aca="false">IFERROR(F134/E134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H134" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="7" t="n">
+        <f aca="false">IFERROR(H134/F134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J134" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="23" t="n">
+        <f aca="false">IFERROR(H134/K134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M134" s="24" t="n">
+        <f aca="false">IFERROR(K134/H134,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N134" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O134" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P134" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="23" t="n">
+        <f aca="false">IFERROR(F135/E135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="7" t="n">
+        <f aca="false">IFERROR(H135/F135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="23" t="n">
+        <f aca="false">IFERROR(H135/K135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M135" s="24" t="n">
+        <f aca="false">IFERROR(K135/H135,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N135" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O135" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P135" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="23" t="n">
+        <f aca="false">IFERROR(F136/E136,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H136" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="7" t="n">
+        <f aca="false">IFERROR(H136/F136,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="23" t="n">
+        <f aca="false">IFERROR(H136/K136,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M136" s="24" t="n">
+        <f aca="false">IFERROR(K136/H136,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N136" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O136" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P136" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="23" t="n">
+        <f aca="false">IFERROR(F137/E137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="7" t="n">
+        <f aca="false">IFERROR(H137/F137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="23" t="n">
+        <f aca="false">IFERROR(H137/K137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M137" s="24" t="n">
+        <f aca="false">IFERROR(K137/H137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N137" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O137" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P137" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="23" t="n">
+        <f aca="false">IFERROR(F138/E138,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="7" t="n">
+        <f aca="false">IFERROR(H138/F138,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="23" t="n">
+        <f aca="false">IFERROR(H138/K138,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M138" s="24" t="n">
+        <f aca="false">IFERROR(K138/H138,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N138" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O138" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P138" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="23" t="n">
+        <f aca="false">IFERROR(F139/E139,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="7" t="n">
+        <f aca="false">IFERROR(H139/F139,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J139" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="23" t="n">
+        <f aca="false">IFERROR(H139/K139,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M139" s="24" t="n">
+        <f aca="false">IFERROR(K139/H139,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N139" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O139" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P139" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="23" t="n">
+        <f aca="false">IFERROR(F140/E140,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="7" t="n">
+        <f aca="false">IFERROR(H140/F140,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J140" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="23" t="n">
+        <f aca="false">IFERROR(H140/K140,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M140" s="24" t="n">
+        <f aca="false">IFERROR(K140/H140,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N140" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O140" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P140" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="23" t="n">
+        <f aca="false">IFERROR(F141/E141,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="7" t="n">
+        <f aca="false">IFERROR(H141/F141,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J141" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="23" t="n">
+        <f aca="false">IFERROR(H141/K141,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M141" s="24" t="n">
+        <f aca="false">IFERROR(K141/H141,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N141" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O141" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P141" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="23" t="n">
+        <f aca="false">IFERROR(F142/E142,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H142" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="7" t="n">
+        <f aca="false">IFERROR(H142/F142,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J142" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="23" t="n">
+        <f aca="false">IFERROR(H142/K142,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M142" s="24" t="n">
+        <f aca="false">IFERROR(K142/H142,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N142" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O142" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P142" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="23" t="n">
+        <f aca="false">IFERROR(F143/E143,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="7" t="n">
+        <f aca="false">IFERROR(H143/F143,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J143" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="23" t="n">
+        <f aca="false">IFERROR(H143/K143,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M143" s="24" t="n">
+        <f aca="false">IFERROR(K143/H143,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N143" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O143" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P143" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="23" t="n">
+        <f aca="false">IFERROR(F144/E144,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H144" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="7" t="n">
+        <f aca="false">IFERROR(H144/F144,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J144" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="23" t="n">
+        <f aca="false">IFERROR(H144/K144,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M144" s="24" t="n">
+        <f aca="false">IFERROR(K144/H144,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N144" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O144" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P144" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="23" t="n">
+        <f aca="false">IFERROR(F145/E145,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="7" t="n">
+        <f aca="false">IFERROR(H145/F145,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J145" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="23" t="n">
+        <f aca="false">IFERROR(H145/K145,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M145" s="24" t="n">
+        <f aca="false">IFERROR(K145/H145,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N145" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="O145" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P145" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="23" t="n">
+        <f aca="false">IFERROR(F146/E146,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="7" t="n">
+        <f aca="false">IFERROR(H146/F146,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="23" t="n">
+        <f aca="false">IFERROR(H146/K146,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M146" s="24" t="n">
+        <f aca="false">IFERROR(K146/H146,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N146" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O146" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P146" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="23" t="n">
+        <f aca="false">IFERROR(F147/E147,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="7" t="n">
+        <f aca="false">IFERROR(H147/F147,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="23" t="n">
+        <f aca="false">IFERROR(H147/K147,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M147" s="24" t="n">
+        <f aca="false">IFERROR(K147/H147,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N147" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O147" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P147" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="E148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="23" t="n">
+        <f aca="false">IFERROR(F148/E148,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H148" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="7" t="n">
+        <f aca="false">IFERROR(H148/F148,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="23" t="n">
+        <f aca="false">IFERROR(H148/K148,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M148" s="24" t="n">
+        <f aca="false">IFERROR(K148/H148,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N148" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O148" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P148" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E149" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="23" t="n">
+        <f aca="false">IFERROR(F149/E149,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="7" t="n">
+        <f aca="false">IFERROR(H149/F149,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="23" t="n">
+        <f aca="false">IFERROR(H149/K149,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M149" s="24" t="n">
+        <f aca="false">IFERROR(K149/H149,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N149" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O149" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P149" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="23" t="n">
+        <f aca="false">IFERROR(F150/E150,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="7" t="n">
+        <f aca="false">IFERROR(H150/F150,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="23" t="n">
+        <f aca="false">IFERROR(H150/K150,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M150" s="24" t="n">
+        <f aca="false">IFERROR(K150/H150,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N150" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O150" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P150" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="23" t="n">
+        <f aca="false">IFERROR(F151/E151,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="7" t="n">
+        <f aca="false">IFERROR(H151/F151,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="23" t="n">
+        <f aca="false">IFERROR(H151/K151,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M151" s="24" t="n">
+        <f aca="false">IFERROR(K151/H151,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N151" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O151" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P151" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E152" s="47" t="n">
+        <f aca="false">SUM(E4:E151)</f>
+        <v>39739</v>
+      </c>
+      <c r="F152" s="47" t="n">
+        <f aca="false">SUM(F4:F151)</f>
+        <v>459</v>
+      </c>
+      <c r="H152" s="48" t="n">
+        <f aca="false">SUM(H4:H151)</f>
+        <v>279.66</v>
+      </c>
+      <c r="J152" s="47" t="n">
+        <f aca="false">SUM(J4:J151)</f>
+        <v>37</v>
+      </c>
+      <c r="K152" s="48" t="n">
+        <f aca="false">SUM(K4:K151)</f>
+        <v>415.79</v>
+      </c>
+      <c r="L152" s="49" t="n">
+        <f aca="false">IFERROR(H152/K152,0)</f>
+        <v>0.672599148608673</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B161" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B162" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B164" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B165" s="2" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/resultados/grupo_pinza_V2.xlsx
+++ b/resultados/grupo_pinza_V2.xlsx
@@ -76,6 +76,30 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">asin="…" es como Amazon escribe una segmentación por producto (así sale en exports y hojas masivas). En la consola NO se escribe así: Campaña 'Pinza - Pruebas' → grupo 'Pruebas - Competencia' → Segmentación → 'Productos individuales' → pestaña 'Introducir lista' → pega solo el código (B07H996QMD) → puja 0,30 €.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">En la consola: misma campaña → Segmentación → pestaña 'Categorías' → busca 'Soportes montados en salpicadero' → 'Refinar': precio desde 12 € y valoración de 0 a 4 estrellas → puja 0,30 €.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="O4" authorId="0">
       <text>
         <r>
@@ -139,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="391">
   <si>
     <t xml:space="preserve">Grupo de anuncios Pinza V2 — plan de cambios y seguimiento</t>
   </si>
@@ -606,7 +630,10 @@
     <t xml:space="preserve">T-018</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL GRUPO</t>
+    <t xml:space="preserve">TOTAL campaña principal (Pinza - Principal V2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL campaña de pruebas (Pinza - Pruebas)</t>
   </si>
   <si>
     <t xml:space="preserve">Seguimiento — una fila por keyword en cada revisión (cada 3 días). Datos ACUMULADOS desde la creación del grupo, copiados del export de Segmentación de Amazon Ads.</t>
@@ -2555,7 +2582,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -3983,11 +4010,11 @@
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
       <c r="E19" s="29" t="n">
-        <f aca="false">SUM(E4:E18)</f>
+        <f aca="false">SUM(E4:E13)</f>
         <v>0</v>
       </c>
       <c r="F19" s="29" t="n">
-        <f aca="false">SUM(F4:F18)</f>
+        <f aca="false">SUM(F4:F13)</f>
         <v>0</v>
       </c>
       <c r="G19" s="30" t="n">
@@ -3995,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="31" t="n">
-        <f aca="false">SUM(H4:H18)</f>
+        <f aca="false">SUM(H4:H13)</f>
         <v>0</v>
       </c>
       <c r="I19" s="31" t="n">
@@ -4003,11 +4030,11 @@
         <v>0</v>
       </c>
       <c r="J19" s="29" t="n">
-        <f aca="false">SUM(J4:J18)</f>
+        <f aca="false">SUM(J4:J13)</f>
         <v>0</v>
       </c>
       <c r="K19" s="31" t="n">
-        <f aca="false">SUM(K4:K18)</f>
+        <f aca="false">SUM(K4:K13)</f>
         <v>0</v>
       </c>
       <c r="L19" s="30" t="n">
@@ -4027,6 +4054,59 @@
       <c r="T19" s="28"/>
       <c r="U19" s="28"/>
       <c r="V19" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28"/>
+      <c r="B20" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29" t="n">
+        <f aca="false">SUM(E14:E18)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <f aca="false">SUM(F14:F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <f aca="false">IFERROR(F20/E20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="31" t="n">
+        <f aca="false">SUM(H14:H18)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="31" t="n">
+        <f aca="false">IFERROR(H20/F20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <f aca="false">SUM(J14:J18)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="31" t="n">
+        <f aca="false">SUM(K14:K18)</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <f aca="false">IFERROR(H20/K20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="32" t="n">
+        <f aca="false">IFERROR(K20/H20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U4:U18">
@@ -4082,12 +4162,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>96</v>
@@ -4132,13 +4212,13 @@
         <v>107</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q3" s="16" t="s">
         <v>117</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4192,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q4" s="4" t="str">
         <f aca="false">IF(B4="","",B4&amp;" | "&amp;C4)</f>
@@ -4254,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q5" s="4" t="str">
         <f aca="false">IF(B5="","",B5&amp;" | "&amp;C5)</f>
@@ -4316,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q6" s="4" t="str">
         <f aca="false">IF(B6="","",B6&amp;" | "&amp;C6)</f>
@@ -4378,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q7" s="4" t="str">
         <f aca="false">IF(B7="","",B7&amp;" | "&amp;C7)</f>
@@ -4440,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q8" s="4" t="str">
         <f aca="false">IF(B8="","",B8&amp;" | "&amp;C8)</f>
@@ -4502,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q9" s="4" t="str">
         <f aca="false">IF(B9="","",B9&amp;" | "&amp;C9)</f>
@@ -4564,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q10" s="4" t="str">
         <f aca="false">IF(B10="","",B10&amp;" | "&amp;C10)</f>
@@ -4626,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q11" s="4" t="str">
         <f aca="false">IF(B11="","",B11&amp;" | "&amp;C11)</f>
@@ -4688,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q12" s="4" t="str">
         <f aca="false">IF(B12="","",B12&amp;" | "&amp;C12)</f>
@@ -4750,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q13" s="4" t="str">
         <f aca="false">IF(B13="","",B13&amp;" | "&amp;C13)</f>
@@ -4812,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q14" s="4" t="str">
         <f aca="false">IF(B14="","",B14&amp;" | "&amp;C14)</f>
@@ -4874,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q15" s="4" t="str">
         <f aca="false">IF(B15="","",B15&amp;" | "&amp;C15)</f>
@@ -4936,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16" s="4" t="str">
         <f aca="false">IF(B16="","",B16&amp;" | "&amp;C16)</f>
@@ -4998,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q17" s="4" t="str">
         <f aca="false">IF(B17="","",B17&amp;" | "&amp;C17)</f>
@@ -5060,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q18" s="4" t="str">
         <f aca="false">IF(B18="","",B18&amp;" | "&amp;C18)</f>
@@ -19754,7 +19834,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19762,76 +19842,76 @@
         <v>113</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>96</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19842,7 +19922,7 @@
         <v>46290</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="39"/>
@@ -19853,12 +19933,12 @@
         <v/>
       </c>
       <c r="I4" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="42"/>
       <c r="K4" s="39"/>
       <c r="L4" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M4" s="44"/>
       <c r="N4" s="40" t="str">
@@ -19911,7 +19991,7 @@
         <v>46290</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>118</v>
@@ -19930,16 +20010,16 @@
         <v>0.258064516129032</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J5" s="42" t="n">
         <v>0.1891</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L5" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M5" s="44"/>
       <c r="N5" s="40" t="str">
@@ -19992,7 +20072,7 @@
         <v>46290</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>122</v>
@@ -20011,16 +20091,16 @@
         <v>0</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J6" s="42" t="n">
         <v>0.3003</v>
       </c>
       <c r="K6" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L6" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M6" s="44"/>
       <c r="N6" s="40" t="str">
@@ -20073,7 +20153,7 @@
         <v>46290</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>125</v>
@@ -20092,16 +20172,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J7" s="42" t="n">
         <v>0.309</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L7" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M7" s="44"/>
       <c r="N7" s="40" t="str">
@@ -20154,7 +20234,7 @@
         <v>46290</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>125</v>
@@ -20173,16 +20253,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J8" s="42" t="n">
         <v>0.316</v>
       </c>
       <c r="K8" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L8" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M8" s="44"/>
       <c r="N8" s="40" t="str">
@@ -20235,7 +20315,7 @@
         <v>46290</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>118</v>
@@ -20254,16 +20334,16 @@
         <v>-0.254545454545455</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J9" s="42" t="n">
         <v>0.4754</v>
       </c>
       <c r="K9" s="39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L9" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M9" s="44"/>
       <c r="N9" s="40" t="str">
@@ -20316,7 +20396,7 @@
         <v>46290</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>130</v>
@@ -20333,7 +20413,7 @@
         <v/>
       </c>
       <c r="I10" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J10" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20343,7 +20423,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M10" s="44"/>
       <c r="N10" s="40" t="str">
@@ -20396,7 +20476,7 @@
         <v>46290</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>133</v>
@@ -20413,7 +20493,7 @@
         <v/>
       </c>
       <c r="I11" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J11" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20423,7 +20503,7 @@
         <v>3</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M11" s="44"/>
       <c r="N11" s="40" t="str">
@@ -20476,7 +20556,7 @@
         <v>46290</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>135</v>
@@ -20493,7 +20573,7 @@
         <v/>
       </c>
       <c r="I12" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J12" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20503,7 +20583,7 @@
         <v>3</v>
       </c>
       <c r="L12" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M12" s="44"/>
       <c r="N12" s="40" t="str">
@@ -20556,7 +20636,7 @@
         <v>46290</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>137</v>
@@ -20573,7 +20653,7 @@
         <v/>
       </c>
       <c r="I13" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J13" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20583,7 +20663,7 @@
         <v>3</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M13" s="44"/>
       <c r="N13" s="40" t="str">
@@ -20636,7 +20716,7 @@
         <v>46290</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>139</v>
@@ -20653,7 +20733,7 @@
         <v/>
       </c>
       <c r="I14" s="19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J14" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20663,7 +20743,7 @@
         <v>3</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M14" s="44"/>
       <c r="N14" s="40" t="str">
@@ -20710,13 +20790,13 @@
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B15" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="39"/>
@@ -20729,12 +20809,12 @@
         <v/>
       </c>
       <c r="I15" s="19" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J15" s="42"/>
       <c r="K15" s="39"/>
       <c r="L15" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" s="44"/>
       <c r="N15" s="40" t="str">
@@ -20781,13 +20861,13 @@
     </row>
     <row r="16" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="39"/>
@@ -20798,12 +20878,12 @@
         <v/>
       </c>
       <c r="I16" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J16" s="42"/>
       <c r="K16" s="39"/>
       <c r="L16" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M16" s="44"/>
       <c r="N16" s="40" t="str">
@@ -20856,7 +20936,7 @@
         <v>46290</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>141</v>
@@ -20873,7 +20953,7 @@
         <v/>
       </c>
       <c r="I17" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J17" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20883,7 +20963,7 @@
         <v>3</v>
       </c>
       <c r="L17" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" s="44"/>
       <c r="N17" s="40" t="str">
@@ -20936,7 +21016,7 @@
         <v>46290</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>145</v>
@@ -20953,7 +21033,7 @@
         <v/>
       </c>
       <c r="I18" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J18" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -20963,7 +21043,7 @@
         <v>3</v>
       </c>
       <c r="L18" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M18" s="44"/>
       <c r="N18" s="40" t="str">
@@ -21016,7 +21096,7 @@
         <v>46290</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>147</v>
@@ -21033,7 +21113,7 @@
         <v/>
       </c>
       <c r="I19" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J19" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -21043,7 +21123,7 @@
         <v>3</v>
       </c>
       <c r="L19" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M19" s="44"/>
       <c r="N19" s="40" t="str">
@@ -21096,7 +21176,7 @@
         <v>46290</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>149</v>
@@ -21113,7 +21193,7 @@
         <v/>
       </c>
       <c r="I20" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J20" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -21123,7 +21203,7 @@
         <v>3</v>
       </c>
       <c r="L20" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M20" s="44"/>
       <c r="N20" s="40" t="str">
@@ -21176,7 +21256,7 @@
         <v>46290</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>151</v>
@@ -21193,7 +21273,7 @@
         <v/>
       </c>
       <c r="I21" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J21" s="42" t="n">
         <f aca="false">Leyenda!$B$5</f>
@@ -21203,7 +21283,7 @@
         <v>3</v>
       </c>
       <c r="L21" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M21" s="44"/>
       <c r="N21" s="40" t="str">
@@ -21250,19 +21330,19 @@
     </row>
     <row r="22" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F22" s="41"/>
       <c r="G22" s="41"/>
@@ -21271,12 +21351,12 @@
         <v/>
       </c>
       <c r="I22" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J22" s="42"/>
       <c r="K22" s="39"/>
       <c r="L22" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M22" s="44"/>
       <c r="N22" s="40" t="str">
@@ -21323,19 +21403,19 @@
     </row>
     <row r="23" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F23" s="41"/>
       <c r="G23" s="41"/>
@@ -21344,12 +21424,12 @@
         <v/>
       </c>
       <c r="I23" s="19" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J23" s="42"/>
       <c r="K23" s="39"/>
       <c r="L23" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M23" s="44"/>
       <c r="N23" s="40" t="str">
@@ -21396,19 +21476,19 @@
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B24" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
@@ -21417,12 +21497,12 @@
         <v/>
       </c>
       <c r="I24" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J24" s="42"/>
       <c r="K24" s="39"/>
       <c r="L24" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M24" s="44"/>
       <c r="N24" s="40" t="str">
@@ -21469,19 +21549,19 @@
     </row>
     <row r="25" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B25" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
@@ -21490,12 +21570,12 @@
         <v/>
       </c>
       <c r="I25" s="19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J25" s="42"/>
       <c r="K25" s="39"/>
       <c r="L25" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M25" s="44"/>
       <c r="N25" s="40" t="str">
@@ -21542,19 +21622,19 @@
     </row>
     <row r="26" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F26" s="41"/>
       <c r="G26" s="41"/>
@@ -21563,12 +21643,12 @@
         <v/>
       </c>
       <c r="I26" s="19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J26" s="42"/>
       <c r="K26" s="39"/>
       <c r="L26" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M26" s="44"/>
       <c r="N26" s="40" t="str">
@@ -21615,19 +21695,19 @@
     </row>
     <row r="27" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="39" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C27" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F27" s="41"/>
       <c r="G27" s="41"/>
@@ -21636,12 +21716,12 @@
         <v/>
       </c>
       <c r="I27" s="19" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J27" s="42"/>
       <c r="K27" s="39"/>
       <c r="L27" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M27" s="44"/>
       <c r="N27" s="40" t="str">
@@ -21688,19 +21768,19 @@
     </row>
     <row r="28" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B28" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F28" s="41"/>
       <c r="G28" s="41"/>
@@ -21709,12 +21789,12 @@
         <v/>
       </c>
       <c r="I28" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J28" s="42"/>
       <c r="K28" s="39"/>
       <c r="L28" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M28" s="44"/>
       <c r="N28" s="40" t="str">
@@ -21761,19 +21841,19 @@
     </row>
     <row r="29" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B29" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F29" s="41"/>
       <c r="G29" s="41"/>
@@ -21782,12 +21862,12 @@
         <v/>
       </c>
       <c r="I29" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J29" s="42"/>
       <c r="K29" s="39"/>
       <c r="L29" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="44"/>
       <c r="N29" s="40" t="str">
@@ -21834,16 +21914,16 @@
     </row>
     <row r="30" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B30" s="40" t="n">
         <v>46290</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E30" s="39" t="s">
         <v>91</v>
@@ -21855,12 +21935,12 @@
         <v/>
       </c>
       <c r="I30" s="19" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J30" s="42"/>
       <c r="K30" s="39"/>
       <c r="L30" s="43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="44"/>
       <c r="N30" s="40" t="str">
@@ -21907,7 +21987,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="43"/>
@@ -21960,7 +22040,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B32" s="44"/>
       <c r="C32" s="43"/>
@@ -22013,7 +22093,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="39" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B33" s="44"/>
       <c r="C33" s="43"/>
@@ -22066,7 +22146,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="39" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B34" s="44"/>
       <c r="C34" s="43"/>
@@ -22119,7 +22199,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B35" s="44"/>
       <c r="C35" s="43"/>
@@ -22172,7 +22252,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B36" s="44"/>
       <c r="C36" s="43"/>
@@ -22225,7 +22305,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="39" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B37" s="44"/>
       <c r="C37" s="43"/>
@@ -22278,7 +22358,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="43"/>
@@ -22331,7 +22411,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="39" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B39" s="44"/>
       <c r="C39" s="43"/>
@@ -22384,7 +22464,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="39" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B40" s="44"/>
       <c r="C40" s="43"/>
@@ -22437,7 +22517,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="39" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B41" s="44"/>
       <c r="C41" s="43"/>
@@ -22490,7 +22570,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="39" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B42" s="44"/>
       <c r="C42" s="43"/>
@@ -22543,7 +22623,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="39" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B43" s="44"/>
       <c r="C43" s="43"/>
@@ -22596,7 +22676,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="39" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B44" s="44"/>
       <c r="C44" s="43"/>
@@ -22649,7 +22729,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="39" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="43"/>
@@ -22702,7 +22782,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B46" s="44"/>
       <c r="C46" s="43"/>
@@ -22755,7 +22835,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B47" s="44"/>
       <c r="C47" s="43"/>
@@ -22808,7 +22888,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B48" s="44"/>
       <c r="C48" s="43"/>
@@ -22861,7 +22941,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B49" s="44"/>
       <c r="C49" s="43"/>
@@ -22914,7 +22994,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B50" s="44"/>
       <c r="C50" s="43"/>
@@ -22967,7 +23047,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B51" s="44"/>
       <c r="C51" s="43"/>
@@ -23020,7 +23100,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="39" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B52" s="44"/>
       <c r="C52" s="43"/>
@@ -23073,7 +23153,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="39" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B53" s="44"/>
       <c r="C53" s="43"/>
@@ -23126,7 +23206,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="39" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B54" s="44"/>
       <c r="C54" s="43"/>
@@ -23179,7 +23259,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="39" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B55" s="44"/>
       <c r="C55" s="43"/>
@@ -23232,7 +23312,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B56" s="44"/>
       <c r="C56" s="43"/>
@@ -23285,7 +23365,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B57" s="44"/>
       <c r="C57" s="43"/>
@@ -23338,7 +23418,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="39" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B58" s="44"/>
       <c r="C58" s="43"/>
@@ -23391,7 +23471,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="39" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B59" s="44"/>
       <c r="C59" s="43"/>
@@ -23444,7 +23524,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="39" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="43"/>
@@ -23497,7 +23577,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="39" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B61" s="44"/>
       <c r="C61" s="43"/>
@@ -23550,7 +23630,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="39" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B62" s="44"/>
       <c r="C62" s="43"/>
@@ -23603,7 +23683,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B63" s="44"/>
       <c r="C63" s="43"/>
@@ -23656,7 +23736,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B64" s="44"/>
       <c r="C64" s="43"/>
@@ -23709,7 +23789,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B65" s="44"/>
       <c r="C65" s="43"/>
@@ -23762,7 +23842,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" s="44"/>
       <c r="C66" s="43"/>
@@ -23815,7 +23895,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" s="44"/>
       <c r="C67" s="43"/>
@@ -23868,7 +23948,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B68" s="44"/>
       <c r="C68" s="43"/>
@@ -23921,7 +24001,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" s="44"/>
       <c r="C69" s="43"/>
@@ -23974,7 +24054,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" s="44"/>
       <c r="C70" s="43"/>
@@ -24027,7 +24107,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="39" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" s="44"/>
       <c r="C71" s="43"/>
@@ -24080,7 +24160,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B72" s="44"/>
       <c r="C72" s="43"/>
@@ -24133,7 +24213,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B73" s="44"/>
       <c r="C73" s="43"/>
@@ -24186,7 +24266,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B74" s="44"/>
       <c r="C74" s="43"/>
@@ -24239,7 +24319,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="39" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B75" s="44"/>
       <c r="C75" s="43"/>
@@ -24292,7 +24372,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="39" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B76" s="44"/>
       <c r="C76" s="43"/>
@@ -24345,7 +24425,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="39" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B77" s="44"/>
       <c r="C77" s="43"/>
@@ -24398,7 +24478,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="39" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B78" s="44"/>
       <c r="C78" s="43"/>
@@ -24451,7 +24531,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="39" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B79" s="44"/>
       <c r="C79" s="43"/>
@@ -24504,7 +24584,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B80" s="44"/>
       <c r="C80" s="43"/>
@@ -24557,7 +24637,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B81" s="44"/>
       <c r="C81" s="43"/>
@@ -24610,7 +24690,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="39" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B82" s="44"/>
       <c r="C82" s="43"/>
@@ -24663,7 +24743,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B83" s="44"/>
       <c r="C83" s="43"/>
@@ -24770,7 +24850,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24814,18 +24894,18 @@
         <v>107</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P3" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>125</v>
@@ -24868,18 +24948,18 @@
         <v>6.14792899408284</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>118</v>
@@ -24922,18 +25002,18 @@
         <v>6.06215213358071</v>
       </c>
       <c r="N5" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>125</v>
@@ -24976,18 +25056,18 @@
         <v>3.63333333333333</v>
       </c>
       <c r="N6" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="P6" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="O6" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>122</v>
@@ -25030,18 +25110,18 @@
         <v>3.33012820512821</v>
       </c>
       <c r="N7" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="P7" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>125</v>
@@ -25084,18 +25164,18 @@
         <v>2.74225941422594</v>
       </c>
       <c r="N8" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="O8" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>118</v>
@@ -25138,18 +25218,18 @@
         <v>2.10341643582641</v>
       </c>
       <c r="N9" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>125</v>
@@ -25192,21 +25272,21 @@
         <v>2.05319440636139</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>119</v>
@@ -25246,21 +25326,21 @@
         <v>0.517702936096719</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>123</v>
@@ -25300,21 +25380,21 @@
         <v>0.341253791708797</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>123</v>
@@ -25354,21 +25434,21 @@
         <v>0</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>126</v>
@@ -25408,21 +25488,21 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="P14" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>123</v>
@@ -25462,21 +25542,21 @@
         <v>0</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>123</v>
@@ -25516,21 +25596,21 @@
         <v>0</v>
       </c>
       <c r="N16" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="P16" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="O16" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>119</v>
@@ -25570,21 +25650,21 @@
         <v>0</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>123</v>
@@ -25624,21 +25704,21 @@
         <v>0</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>123</v>
@@ -25678,18 +25758,18 @@
         <v>0</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>118</v>
@@ -25732,21 +25812,21 @@
         <v>0</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>123</v>
@@ -25786,18 +25866,18 @@
         <v>0</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>118</v>
@@ -25840,21 +25920,21 @@
         <v>0</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>123</v>
@@ -25894,21 +25974,21 @@
         <v>0</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>119</v>
@@ -25948,21 +26028,21 @@
         <v>0</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>123</v>
@@ -26002,21 +26082,21 @@
         <v>0</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>123</v>
@@ -26056,21 +26136,21 @@
         <v>0</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>119</v>
@@ -26110,21 +26190,21 @@
         <v>0</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>123</v>
@@ -26164,21 +26244,21 @@
         <v>0</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>123</v>
@@ -26218,21 +26298,21 @@
         <v>0</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>123</v>
@@ -26272,18 +26352,18 @@
         <v>0</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>125</v>
@@ -26326,21 +26406,21 @@
         <v>0</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>119</v>
@@ -26380,21 +26460,21 @@
         <v>0</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>126</v>
@@ -26434,21 +26514,21 @@
         <v>0</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>123</v>
@@ -26488,21 +26568,21 @@
         <v>0</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>123</v>
@@ -26542,18 +26622,18 @@
         <v>0</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>118</v>
@@ -26596,21 +26676,21 @@
         <v>0</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>123</v>
@@ -26650,21 +26730,21 @@
         <v>0</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>119</v>
@@ -26704,21 +26784,21 @@
         <v>0</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>123</v>
@@ -26758,21 +26838,21 @@
         <v>0</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>119</v>
@@ -26812,21 +26892,21 @@
         <v>0</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>123</v>
@@ -26866,21 +26946,21 @@
         <v>0</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>123</v>
@@ -26920,21 +27000,21 @@
         <v>0</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>119</v>
@@ -26974,18 +27054,18 @@
         <v>0</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>118</v>
@@ -27028,21 +27108,21 @@
         <v>0</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>123</v>
@@ -27082,21 +27162,21 @@
         <v>0</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>123</v>
@@ -27136,21 +27216,21 @@
         <v>0</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>123</v>
@@ -27190,18 +27270,18 @@
         <v>0</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>125</v>
@@ -27244,21 +27324,21 @@
         <v>0</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>123</v>
@@ -27298,21 +27378,21 @@
         <v>0</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>123</v>
@@ -27352,21 +27432,21 @@
         <v>0</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>123</v>
@@ -27406,21 +27486,21 @@
         <v>0</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>123</v>
@@ -27460,21 +27540,21 @@
         <v>0</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>123</v>
@@ -27514,21 +27594,21 @@
         <v>0</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>123</v>
@@ -27568,21 +27648,21 @@
         <v>0</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>123</v>
@@ -27622,21 +27702,21 @@
         <v>0</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>123</v>
@@ -27676,21 +27756,21 @@
         <v>0</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>123</v>
@@ -27730,21 +27810,21 @@
         <v>0</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>123</v>
@@ -27784,21 +27864,21 @@
         <v>0</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>119</v>
@@ -27838,21 +27918,21 @@
         <v>0</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>123</v>
@@ -27892,21 +27972,21 @@
         <v>0</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>123</v>
@@ -27946,21 +28026,21 @@
         <v>0</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>123</v>
@@ -28000,21 +28080,21 @@
         <v>0</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>123</v>
@@ -28054,21 +28134,21 @@
         <v>0</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>123</v>
@@ -28108,21 +28188,21 @@
         <v>0</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>123</v>
@@ -28162,21 +28242,21 @@
         <v>0</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>123</v>
@@ -28216,21 +28296,21 @@
         <v>0</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>123</v>
@@ -28270,21 +28350,21 @@
         <v>0</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>123</v>
@@ -28324,21 +28404,21 @@
         <v>0</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>126</v>
@@ -28378,21 +28458,21 @@
         <v>0</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>123</v>
@@ -28432,21 +28512,21 @@
         <v>0</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>119</v>
@@ -28486,21 +28566,21 @@
         <v>0</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>119</v>
@@ -28540,21 +28620,21 @@
         <v>0</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>126</v>
@@ -28594,21 +28674,21 @@
         <v>0</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>123</v>
@@ -28648,21 +28728,21 @@
         <v>0</v>
       </c>
       <c r="N74" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>123</v>
@@ -28702,21 +28782,21 @@
         <v>0</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>119</v>
@@ -28756,21 +28836,21 @@
         <v>0</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>119</v>
@@ -28810,21 +28890,21 @@
         <v>0</v>
       </c>
       <c r="N77" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>126</v>
@@ -28864,21 +28944,21 @@
         <v>0</v>
       </c>
       <c r="N78" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>123</v>
@@ -28918,21 +28998,21 @@
         <v>0</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>119</v>
@@ -28972,21 +29052,21 @@
         <v>0</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>126</v>
@@ -29026,21 +29106,21 @@
         <v>0</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>126</v>
@@ -29080,21 +29160,21 @@
         <v>0</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>123</v>
@@ -29134,21 +29214,21 @@
         <v>0</v>
       </c>
       <c r="N83" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>123</v>
@@ -29188,21 +29268,21 @@
         <v>0</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>126</v>
@@ -29242,21 +29322,21 @@
         <v>0</v>
       </c>
       <c r="N85" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>119</v>
@@ -29296,21 +29376,21 @@
         <v>0</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>123</v>
@@ -29350,21 +29430,21 @@
         <v>0</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>123</v>
@@ -29404,21 +29484,21 @@
         <v>0</v>
       </c>
       <c r="N88" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>119</v>
@@ -29458,21 +29538,21 @@
         <v>0</v>
       </c>
       <c r="N89" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>123</v>
@@ -29512,21 +29592,21 @@
         <v>0</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>123</v>
@@ -29566,21 +29646,21 @@
         <v>0</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>123</v>
@@ -29620,21 +29700,21 @@
         <v>0</v>
       </c>
       <c r="N92" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>119</v>
@@ -29674,21 +29754,21 @@
         <v>0</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>123</v>
@@ -29728,21 +29808,21 @@
         <v>0</v>
       </c>
       <c r="N94" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>119</v>
@@ -29782,21 +29862,21 @@
         <v>0</v>
       </c>
       <c r="N95" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>123</v>
@@ -29836,21 +29916,21 @@
         <v>0</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>126</v>
@@ -29890,21 +29970,21 @@
         <v>0</v>
       </c>
       <c r="N97" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>119</v>
@@ -29944,21 +30024,21 @@
         <v>0</v>
       </c>
       <c r="N98" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>123</v>
@@ -29998,21 +30078,21 @@
         <v>0</v>
       </c>
       <c r="N99" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>126</v>
@@ -30052,21 +30132,21 @@
         <v>0</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>119</v>
@@ -30106,21 +30186,21 @@
         <v>0</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P101" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>123</v>
@@ -30160,21 +30240,21 @@
         <v>0</v>
       </c>
       <c r="N102" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>123</v>
@@ -30214,21 +30294,21 @@
         <v>0</v>
       </c>
       <c r="N103" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P103" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>119</v>
@@ -30268,21 +30348,21 @@
         <v>0</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>119</v>
@@ -30322,21 +30402,21 @@
         <v>0</v>
       </c>
       <c r="N105" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>123</v>
@@ -30376,21 +30456,21 @@
         <v>0</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P106" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>119</v>
@@ -30430,21 +30510,21 @@
         <v>0</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P107" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>123</v>
@@ -30484,21 +30564,21 @@
         <v>0</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P108" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>119</v>
@@ -30538,21 +30618,21 @@
         <v>0</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P109" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>126</v>
@@ -30592,21 +30672,21 @@
         <v>0</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P110" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>119</v>
@@ -30646,21 +30726,21 @@
         <v>0</v>
       </c>
       <c r="N111" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P111" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>123</v>
@@ -30700,21 +30780,21 @@
         <v>0</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P112" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>119</v>
@@ -30754,21 +30834,21 @@
         <v>0</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>123</v>
@@ -30808,21 +30888,21 @@
         <v>0</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P114" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>126</v>
@@ -30862,21 +30942,21 @@
         <v>0</v>
       </c>
       <c r="N115" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P115" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>119</v>
@@ -30916,21 +30996,21 @@
         <v>0</v>
       </c>
       <c r="N116" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P116" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>123</v>
@@ -30970,21 +31050,21 @@
         <v>0</v>
       </c>
       <c r="N117" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P117" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>126</v>
@@ -31024,21 +31104,21 @@
         <v>0</v>
       </c>
       <c r="N118" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>119</v>
@@ -31078,21 +31158,21 @@
         <v>0</v>
       </c>
       <c r="N119" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P119" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>126</v>
@@ -31132,21 +31212,21 @@
         <v>0</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P120" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>119</v>
@@ -31186,21 +31266,21 @@
         <v>0</v>
       </c>
       <c r="N121" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P121" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>123</v>
@@ -31240,21 +31320,21 @@
         <v>0</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P122" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>126</v>
@@ -31294,21 +31374,21 @@
         <v>0</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>119</v>
@@ -31348,21 +31428,21 @@
         <v>0</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P124" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>123</v>
@@ -31402,21 +31482,21 @@
         <v>0</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P125" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>126</v>
@@ -31456,21 +31536,21 @@
         <v>0</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P126" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>123</v>
@@ -31510,21 +31590,21 @@
         <v>0</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P127" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>123</v>
@@ -31564,21 +31644,21 @@
         <v>0</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P128" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>123</v>
@@ -31618,21 +31698,21 @@
         <v>0</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P129" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>123</v>
@@ -31672,21 +31752,21 @@
         <v>0</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P130" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>123</v>
@@ -31726,21 +31806,21 @@
         <v>0</v>
       </c>
       <c r="N131" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P131" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>123</v>
@@ -31780,21 +31860,21 @@
         <v>0</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P132" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>123</v>
@@ -31834,21 +31914,21 @@
         <v>0</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P133" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>123</v>
@@ -31888,21 +31968,21 @@
         <v>0</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P134" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>123</v>
@@ -31942,21 +32022,21 @@
         <v>0</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>123</v>
@@ -31996,21 +32076,21 @@
         <v>0</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P136" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>123</v>
@@ -32050,21 +32130,21 @@
         <v>0</v>
       </c>
       <c r="N137" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P137" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>123</v>
@@ -32104,21 +32184,21 @@
         <v>0</v>
       </c>
       <c r="N138" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P138" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>123</v>
@@ -32158,21 +32238,21 @@
         <v>0</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P139" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>123</v>
@@ -32212,21 +32292,21 @@
         <v>0</v>
       </c>
       <c r="N140" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>123</v>
@@ -32266,21 +32346,21 @@
         <v>0</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P141" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>123</v>
@@ -32320,21 +32400,21 @@
         <v>0</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>123</v>
@@ -32374,21 +32454,21 @@
         <v>0</v>
       </c>
       <c r="N143" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>123</v>
@@ -32428,21 +32508,21 @@
         <v>0</v>
       </c>
       <c r="N144" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P144" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>123</v>
@@ -32482,21 +32562,21 @@
         <v>0</v>
       </c>
       <c r="N145" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P145" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>123</v>
@@ -32536,21 +32616,21 @@
         <v>0</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>123</v>
@@ -32590,21 +32670,21 @@
         <v>0</v>
       </c>
       <c r="N147" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>123</v>
@@ -32644,18 +32724,18 @@
         <v>0</v>
       </c>
       <c r="N148" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>122</v>
@@ -32698,21 +32778,21 @@
         <v>0</v>
       </c>
       <c r="N149" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P149" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>119</v>
@@ -32752,21 +32832,21 @@
         <v>0</v>
       </c>
       <c r="N150" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P150" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>119</v>
@@ -32806,18 +32886,18 @@
         <v>0</v>
       </c>
       <c r="N151" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P151" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E152" s="49" t="n">
         <f aca="false">SUM(E4:E151)</f>
@@ -32846,62 +32926,62 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B161" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/resultados/grupo_pinza_V2.xlsx
+++ b/resultados/grupo_pinza_V2.xlsx
@@ -38,7 +38,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Es la campaña donde la pinza ha vendido (grupo 'Pinza', 99% del gasto de la pinza). Su grupo antiguo 'Pinza' tiene estas mismas keywords: debe seguir EN PAUSA para no pujar contra ti mismo. Alternativa: campaña nueva solo para este grupo (control de presupuesto más limpio).</t>
+          <t xml:space="preserve">Campaña nueva (presupuesto propio de ~1,67 €/día). La antigua 'Soporte móvil pinza' (ID A0335903WCRWL9CYXAOF) tiene estas mismas keywords en su grupo 'Pinza': debe seguir EN PAUSA para no pujar contra ti mismo.</t>
         </r>
       </text>
     </comment>
@@ -315,7 +315,7 @@
     <t xml:space="preserve">Campaña</t>
   </si>
   <si>
-    <t xml:space="preserve">Soporte móvil pinza  (ID A0335903WCRWL9CYXAOF)</t>
+    <t xml:space="preserve">Pinza - Principal V2 (NUEVA, se crea con resultados/hoja_masiva_pinza_V2.xlsx)</t>
   </si>
   <si>
     <t xml:space="preserve">Tipo de campaña</t>
@@ -726,7 +726,7 @@
     <t xml:space="preserve">Crear grupo de anuncios</t>
   </si>
   <si>
-    <t xml:space="preserve">Crear 'Pinza - Principal V2' con el anuncio B0DCZS1NR6 (O8-5W7J-DSK1) y las 10 keywords de T-002…T-011. Objetivo: concentrar el gasto en lo que ya vende y en 5 frases nuevas con alta intención, con ACOS ≤ 35%.</t>
+    <t xml:space="preserve">Crear la campaña y el grupo 'Pinza - Principal V2' (hoja masiva) con el anuncio B0DCZS1NR6 (O8-5W7J-DSK1) y las 10 keywords de T-002…T-011. Objetivo: concentrar el gasto en lo que ya vende y en 5 frases nuevas con alta intención, con ACOS ≤ 35%.</t>
   </si>
   <si>
     <t xml:space="preserve">Pendiente de aplicar</t>
